--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -3,15 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE49B1CF-A56A-4161-AC51-867F34E9D5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2626746-586E-403B-87A8-8A146426B7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
-    <sheet name="Login" sheetId="3" r:id="rId3"/>
+    <sheet name="Inventory" sheetId="4" r:id="rId3"/>
+    <sheet name="Login" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="330">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -47,9 +51,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Requirements ID</t>
-  </si>
-  <si>
     <t>Assigned To</t>
   </si>
   <si>
@@ -65,7 +66,7 @@
     <t>Jeevan</t>
   </si>
   <si>
-    <t>SD_TS_00</t>
+    <t>SD_TS_002</t>
   </si>
   <si>
     <t>Product Listing</t>
@@ -74,12 +75,18 @@
     <t>Verify inventory page displays all products, prices and images</t>
   </si>
   <si>
+    <t>SD_TS_003</t>
+  </si>
+  <si>
     <t>Product Sorting</t>
   </si>
   <si>
     <t>Verify sorting by Name A-Z, Z-A, Price Low-High and High-Low</t>
   </si>
   <si>
+    <t>SD_TS_004</t>
+  </si>
+  <si>
     <t>Add to Cart</t>
   </si>
   <si>
@@ -89,90 +96,144 @@
     <t>Rudraraj</t>
   </si>
   <si>
+    <t>SD_TS_005</t>
+  </si>
+  <si>
     <t>Remove from Cart</t>
   </si>
   <si>
     <t>Verify removing products from inventory and cart page</t>
   </si>
   <si>
+    <t>SD_TS_006</t>
+  </si>
+  <si>
     <t>Shopping Cart</t>
   </si>
   <si>
     <t>Verify cart badge, cart contents and continue shopping</t>
   </si>
   <si>
+    <t>SD_TS_007</t>
+  </si>
+  <si>
     <t>Checkout Information</t>
   </si>
   <si>
     <t>Validate checkout information form</t>
   </si>
   <si>
+    <t>SD_TS_008</t>
+  </si>
+  <si>
     <t>Checkout Overview</t>
   </si>
   <si>
     <t>Verify product summary, taxes and total price</t>
   </si>
   <si>
+    <t>SD_TS_009</t>
+  </si>
+  <si>
     <t>Order Completion</t>
   </si>
   <si>
     <t>Verify successful order placement</t>
   </si>
   <si>
+    <t>SD_TS_010</t>
+  </si>
+  <si>
     <t>Logout</t>
   </si>
   <si>
     <t>Verify successful logout</t>
   </si>
   <si>
+    <t>SD_TS_011</t>
+  </si>
+  <si>
     <t>Reset App State</t>
   </si>
   <si>
     <t>Verify cart is cleared after reset app state</t>
   </si>
   <si>
+    <t>SD_TS_012</t>
+  </si>
+  <si>
+    <t>Product Details</t>
+  </si>
+  <si>
+    <t>Verify product details page</t>
+  </si>
+  <si>
+    <t>SD_TS_013</t>
+  </si>
+  <si>
     <t>Navigation</t>
   </si>
   <si>
     <t>Verify navigation between pages</t>
   </si>
   <si>
+    <t>SD_TS_014</t>
+  </si>
+  <si>
     <t>Error Messages</t>
   </si>
   <si>
     <t>Verify all validation and login error messages</t>
   </si>
   <si>
+    <t>SD_TS_015</t>
+  </si>
+  <si>
     <t>UI Validation</t>
   </si>
   <si>
     <t>Verify logos, buttons, labels and page layout</t>
   </si>
   <si>
+    <t>SD_TS_016</t>
+  </si>
+  <si>
     <t>Session Management</t>
   </si>
   <si>
     <t>Verify session after refresh and logout</t>
   </si>
   <si>
+    <t>SD_TS_017</t>
+  </si>
+  <si>
     <t>Browser Compatibility</t>
   </si>
   <si>
     <t>Verify application works in Chrome, Firefox and Edge</t>
   </si>
   <si>
+    <t>SD_TS_018</t>
+  </si>
+  <si>
     <t>Performance</t>
   </si>
   <si>
     <t>Verify application loading time</t>
   </si>
   <si>
+    <t>SD_TS_019</t>
+  </si>
+  <si>
     <t>Accessibility</t>
   </si>
   <si>
     <t>Verify keyboard navigation and focus</t>
   </si>
   <si>
+    <t>SD_TS_020</t>
+  </si>
+  <si>
     <t>End-to-End Flow</t>
   </si>
   <si>
@@ -182,6 +243,9 @@
     <t xml:space="preserve">Sauce Demo Test Cases </t>
   </si>
   <si>
+    <t>Reference ID</t>
+  </si>
+  <si>
     <t>Test Case ID</t>
   </si>
   <si>
@@ -203,18 +267,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>PASS / FAIL</t>
-  </si>
-  <si>
-    <t>Defect ID</t>
-  </si>
-  <si>
-    <t>Reference ID</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
+    <t>SD_TS_001
+User Login</t>
+  </si>
+  <si>
     <t>SD_TC_001</t>
   </si>
   <si>
@@ -290,81 +349,670 @@
     <t>Enter locked username &amp; correct password → Click Login</t>
   </si>
   <si>
+    <t>SD_TS_002
+Product Listing</t>
+  </si>
+  <si>
     <t>SD_TC_006</t>
   </si>
   <si>
+    <t>Verify all products displayed</t>
+  </si>
+  <si>
+    <t>Login successful</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Open inventory</t>
+  </si>
+  <si>
+    <t>All six products displayed</t>
+  </si>
+  <si>
     <t>SD_TC_007</t>
   </si>
   <si>
+    <t>Verify product names</t>
+  </si>
+  <si>
+    <t>Names visible</t>
+  </si>
+  <si>
     <t>SD_TC_008</t>
   </si>
   <si>
+    <t>Verify product prices</t>
+  </si>
+  <si>
+    <t>Prices visible</t>
+  </si>
+  <si>
     <t>SD_TC_009</t>
   </si>
   <si>
+    <t>Verify product images</t>
+  </si>
+  <si>
+    <t>Images displayed</t>
+  </si>
+  <si>
+    <t>SD_TS_003
+Product Sorting</t>
+  </si>
+  <si>
     <t>SD_TC_010</t>
   </si>
   <si>
+    <t>Verify sort A-Z</t>
+  </si>
+  <si>
+    <t>Name A-Z</t>
+  </si>
+  <si>
+    <t>Select sort</t>
+  </si>
+  <si>
+    <t>Products sorted alphabetically</t>
+  </si>
+  <si>
     <t>SD_TC_011</t>
   </si>
   <si>
+    <t>Verify sort Z-A</t>
+  </si>
+  <si>
+    <t>Name Z-A</t>
+  </si>
+  <si>
+    <t>Products sorted reverse alphabetically</t>
+  </si>
+  <si>
     <t>SD_TC_012</t>
   </si>
   <si>
+    <t>Verify Price Low-High</t>
+  </si>
+  <si>
+    <t>Low-High</t>
+  </si>
+  <si>
+    <t>Products sorted by price</t>
+  </si>
+  <si>
     <t>SD_TC_013</t>
   </si>
   <si>
+    <t>Verify Price High-Low</t>
+  </si>
+  <si>
+    <t>High-Low</t>
+  </si>
+  <si>
+    <t>SD_TS_004
+Add to Cart</t>
+  </si>
+  <si>
     <t>SD_TC_014</t>
   </si>
   <si>
+    <t>Add single product</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>Click Add to Cart</t>
+  </si>
+  <si>
     <t>SD_TC_015</t>
   </si>
   <si>
+    <t>Add multiple products</t>
+  </si>
+  <si>
+    <t>3 Products</t>
+  </si>
+  <si>
+    <t>Add products</t>
+  </si>
+  <si>
+    <t>SD_TS_005
+Remove from Cart</t>
+  </si>
+  <si>
     <t>SD_TC_016</t>
   </si>
   <si>
+    <t>Remove product</t>
+  </si>
+  <si>
+    <t>Product added</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>SD_TS_006
+Remove from Cart</t>
+  </si>
+  <si>
     <t>SD_TC_017</t>
   </si>
   <si>
+    <t>Verify cart page</t>
+  </si>
+  <si>
+    <t>Cart page</t>
+  </si>
+  <si>
+    <t>Open cart</t>
+  </si>
+  <si>
     <t>SD_TC_018</t>
   </si>
   <si>
+    <t>Continue shopping</t>
+  </si>
+  <si>
+    <t>Click Continue Shopping</t>
+  </si>
+  <si>
+    <t>SD_TS_007
+Checkout Information</t>
+  </si>
+  <si>
     <t>SD_TC_019</t>
   </si>
   <si>
+    <t>Checkout with valid details</t>
+  </si>
+  <si>
+    <t>Checkout page</t>
+  </si>
+  <si>
+    <t>John, Doe, 560001</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
     <t>SD_TC_020</t>
   </si>
   <si>
+    <t>Checkout without first name</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
     <t>SD_TC_021</t>
   </si>
   <si>
+    <t>Checkout without last name</t>
+  </si>
+  <si>
     <t>SD_TC_022</t>
   </si>
   <si>
+    <t>Checkout without zip code</t>
+  </si>
+  <si>
+    <t>SD_TS_008
+Checkout Overview</t>
+  </si>
+  <si>
     <t>SD_TC_023</t>
   </si>
   <si>
+    <t>Verify order summary</t>
+  </si>
+  <si>
+    <t>Overview page</t>
+  </si>
+  <si>
+    <t>SD_TS_009
+Order Completion</t>
+  </si>
+  <si>
     <t>SD_TC_024</t>
   </si>
   <si>
+    <t>Finish checkout</t>
+  </si>
+  <si>
+    <t>Click Finish</t>
+  </si>
+  <si>
+    <t>SD_TS_010
+Logout</t>
+  </si>
+  <si>
     <t>SD_TC_025</t>
   </si>
   <si>
+    <t>User logged in</t>
+  </si>
+  <si>
+    <t>Menu → Logout</t>
+  </si>
+  <si>
+    <t>SD_TS_011
+Reset App State</t>
+  </si>
+  <si>
     <t>SD_TC_026</t>
   </si>
   <si>
     <t>SD_TC_027</t>
   </si>
   <si>
+    <t>Verify page refresh</t>
+  </si>
+  <si>
+    <t>Refresh page</t>
+  </si>
+  <si>
+    <t>SD_TS_012
+Product Details</t>
+  </si>
+  <si>
     <t>SD_TC_028</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify product details page </t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Click product name</t>
+  </si>
+  <si>
     <t>SD_TC_029</t>
   </si>
   <si>
+    <t>Verify product image on details page</t>
+  </si>
+  <si>
+    <t>Any product</t>
+  </si>
+  <si>
+    <t>Open product details</t>
+  </si>
+  <si>
+    <t>SD_TS_013
+Navigation</t>
+  </si>
+  <si>
     <t>SD_TC_030</t>
   </si>
   <si>
+    <t>Verify Add to Cart from product details</t>
+  </si>
+  <si>
+    <t>Open details → Click Add to Cart</t>
+  </si>
+  <si>
+    <t>SD_TC_031</t>
+  </si>
+  <si>
+    <t>Verify Remove button on product details</t>
+  </si>
+  <si>
+    <t>Click Remove</t>
+  </si>
+  <si>
+    <t>SD_TC_032</t>
+  </si>
+  <si>
+    <t>Verify Back to Products button</t>
+  </si>
+  <si>
+    <t>Product details page</t>
+  </si>
+  <si>
+    <t>Click Back to Products</t>
+  </si>
+  <si>
+    <t>SD_TC_033</t>
+  </si>
+  <si>
+    <t>Verify Inventory to Cart navigation</t>
+  </si>
+  <si>
+    <t>Click Cart icon</t>
+  </si>
+  <si>
+    <t>SD_TC_034</t>
+  </si>
+  <si>
+    <t>Verify Cart to Inventory navigation</t>
+  </si>
+  <si>
+    <t>SD_TC_035</t>
+  </si>
+  <si>
+    <t>Verify Checkout navigation</t>
+  </si>
+  <si>
+    <t>Cart contains product</t>
+  </si>
+  <si>
+    <t>Click Checkout</t>
+  </si>
+  <si>
+    <t>SD_TC_036</t>
+  </si>
+  <si>
+    <t>Verify Back Home navigation</t>
+  </si>
+  <si>
+    <t>Order completed</t>
+  </si>
+  <si>
+    <t>Click Back Home</t>
+  </si>
+  <si>
+    <t>SD_TC_037</t>
+  </si>
+  <si>
+    <t>Verify Logout navigation</t>
+  </si>
+  <si>
+    <t>SD_TS_014
+Error Messages</t>
+  </si>
+  <si>
+    <t>SD_TC_038</t>
+  </si>
+  <si>
+    <t>Verify invalid login error message</t>
+  </si>
+  <si>
+    <t>Login page</t>
+  </si>
+  <si>
+    <t>Invalid credentials</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>SD_TC_039</t>
+  </si>
+  <si>
+    <t>Verify empty username error</t>
+  </si>
+  <si>
+    <t>Blank username</t>
+  </si>
+  <si>
+    <t>Click Login</t>
+  </si>
+  <si>
+    <t>SD_TC_040</t>
+  </si>
+  <si>
+    <t>Verify empty password error</t>
+  </si>
+  <si>
+    <t>Blank password</t>
+  </si>
+  <si>
+    <t>SD_TC_041</t>
+  </si>
+  <si>
+    <t>Verify locked user error message</t>
+  </si>
+  <si>
+    <t>locked_out_user</t>
+  </si>
+  <si>
+    <t>SD_TS_015
+UI Validation</t>
+  </si>
+  <si>
+    <t>SD_TC_042</t>
+  </si>
+  <si>
+    <t>Verify checkout validation message</t>
+  </si>
+  <si>
+    <t>Blank fields</t>
+  </si>
+  <si>
+    <t>Click Continue</t>
+  </si>
+  <si>
+    <t>SD_TC_043</t>
+  </si>
+  <si>
+    <t>Verify SauceDemo logo</t>
+  </si>
+  <si>
+    <t>Open application</t>
+  </si>
+  <si>
+    <t>SD_TC_044</t>
+  </si>
+  <si>
+    <t>Verify Login button alignment</t>
+  </si>
+  <si>
+    <t>Observe UI</t>
+  </si>
+  <si>
+    <t>SD_TC_045</t>
+  </si>
+  <si>
+    <t>Verify Product page layout</t>
+  </si>
+  <si>
+    <t>Inventory page</t>
+  </si>
+  <si>
+    <t>Observe page</t>
+  </si>
+  <si>
+    <t>SD_TC_046</t>
+  </si>
+  <si>
+    <t>Verify Cart icon visibility</t>
+  </si>
+  <si>
+    <t>SD_TC_047</t>
+  </si>
+  <si>
+    <t>Verify Footer links</t>
+  </si>
+  <si>
+    <t>Click social media icons</t>
+  </si>
+  <si>
+    <t>SD_TS_016
+Session Management</t>
+  </si>
+  <si>
+    <t>SD_TC_048</t>
+  </si>
+  <si>
+    <t>Verify session after browser refresh</t>
+  </si>
+  <si>
+    <t>Refresh browser</t>
+  </si>
+  <si>
+    <t>SD_TC_049</t>
+  </si>
+  <si>
+    <t>Verify session after navigating pages</t>
+  </si>
+  <si>
+    <t>Navigate between pages</t>
+  </si>
+  <si>
+    <t>SD_TC_050</t>
+  </si>
+  <si>
+    <t>Verify direct access after logout</t>
+  </si>
+  <si>
+    <t>Logged out</t>
+  </si>
+  <si>
+    <t>Inventory URL</t>
+  </si>
+  <si>
+    <t>Enter inventory URL</t>
+  </si>
+  <si>
+    <t>SD_TS_017
+Browser Compatibility</t>
+  </si>
+  <si>
+    <t>SD_TC_051</t>
+  </si>
+  <si>
+    <t>Verify application in Chrome</t>
+  </si>
+  <si>
+    <t>Chrome browser</t>
+  </si>
+  <si>
+    <t>Execute test</t>
+  </si>
+  <si>
+    <t>SD_TC_052</t>
+  </si>
+  <si>
+    <t>Verify application in Firefox</t>
+  </si>
+  <si>
+    <t>Firefox browser</t>
+  </si>
+  <si>
+    <t>SD_TC_053</t>
+  </si>
+  <si>
+    <t>Verify application in Edge</t>
+  </si>
+  <si>
+    <t>Edge browser</t>
+  </si>
+  <si>
+    <t>SD_TS_018
+Performance</t>
+  </si>
+  <si>
+    <t>SD_TC_054</t>
+  </si>
+  <si>
+    <t>Verify Login page load time</t>
+  </si>
+  <si>
+    <t>Application launched</t>
+  </si>
+  <si>
+    <t>Open Login page</t>
+  </si>
+  <si>
+    <t>SD_TC_055</t>
+  </si>
+  <si>
+    <t>Verify Inventory page load time</t>
+  </si>
+  <si>
+    <t>SD_TC_056</t>
+  </si>
+  <si>
+    <t>Verify Checkout completion time</t>
+  </si>
+  <si>
+    <t>SD_TS_019
+Accessibility</t>
+  </si>
+  <si>
+    <t>SD_TC_057</t>
+  </si>
+  <si>
+    <t>Verify keyboard navigation</t>
+  </si>
+  <si>
+    <t>Use Tab key</t>
+  </si>
+  <si>
+    <t>SD_TC_058</t>
+  </si>
+  <si>
+    <t>Verify Login button using keyboard</t>
+  </si>
+  <si>
+    <t>Valid credentials</t>
+  </si>
+  <si>
+    <t>Press Enter</t>
+  </si>
+  <si>
+    <t>SD_TC_059</t>
+  </si>
+  <si>
+    <t>Verify screen readability</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>Check labels and text</t>
+  </si>
+  <si>
+    <t>SD_TS_020
+End-to-End Flow</t>
+  </si>
+  <si>
+    <t>SD_TC_060</t>
+  </si>
+  <si>
+    <t>End-to-End purchase</t>
+  </si>
+  <si>
+    <t>Login → Add → Checkout → Logout</t>
+  </si>
+  <si>
+    <t>Standard User</t>
+  </si>
+  <si>
+    <t>Complete purchase flow</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Image URL</t>
+  </si>
+  <si>
+    <t>A-Z</t>
+  </si>
+  <si>
+    <t>Z-A</t>
+  </si>
+  <si>
+    <t>Low - High</t>
+  </si>
+  <si>
+    <t>High - Low</t>
+  </si>
+  <si>
+    <t>Execution Time</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
     <t>TC_ID</t>
   </si>
   <si>
@@ -396,9 +1044,6 @@
   </si>
   <si>
     <t>USERNAME_REQUIRED</t>
-  </si>
-  <si>
-    <t>locked_out_user</t>
   </si>
   <si>
     <t>LOCKED_USER</t>
@@ -415,12 +1060,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF833C0C"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -461,6 +1100,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -476,7 +1122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -500,7 +1146,35 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -512,9 +1186,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -534,11 +1206,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -546,62 +1311,487 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -612,6 +1802,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{60D95358-8BC2-426A-AC6B-A25958DFDA4B}" name="Table5" displayName="Table5" ref="A2:D22" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16">
+  <autoFilter ref="A2:D22" xr:uid="{60D95358-8BC2-426A-AC6B-A25958DFDA4B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{76067BBC-1BF6-439B-8681-5FE715345014}" name="Scenario #" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{0AB4DB67-5052-4173-93D3-21EB00F3B8C3}" name="Scenario " dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{1E1B0388-9A2B-453D-B7F7-7D7D075E3BE5}" name="Description" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{0E93EF9E-7351-46CA-AA75-9A5B9FB1B8E6}" name="Assigned To" dataDxfId="11"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{45CE1F2E-EBA4-4385-A3B4-74FB8A73B512}" name="Table4" displayName="Table4" ref="B2:I62" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="B2:I62" xr:uid="{45CE1F2E-EBA4-4385-A3B4-74FB8A73B512}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{6993322D-AE1A-4215-B0E9-2BF71122627B}" name="Test Case ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{6EAF7135-414E-4563-9CD5-4978DCEC9AE6}" name="Test Case" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{EEFB54B5-F1A5-4B07-8BB6-3D1DB9569F40}" name="Pre-Requisite" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{6713D2FD-1F5C-482F-9372-F4DAD5E68E18}" name="Test Data" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{379C72D8-A7DF-4C6B-8122-1121A653FAA2}" name="Test Steps" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{E2DC048D-F96E-4433-904F-9568BA956D17}" name="Expected Result" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{B3EABA99-923F-493D-9582-1022B87307F0}" name="Actual Result" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{1D3096A7-8C8C-4B25-A426-410EE6E1576B}" name="Remarks" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -911,390 +2131,335 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="35.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="50" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" s="14" customFormat="1" ht="16.5">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+    </row>
+    <row r="2" spans="1:4" s="16" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="13" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A4" s="33" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="45.75">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A5" s="33" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45.75">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30.75">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A6" s="33" t="s">
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
+      <c r="C6" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30.75">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45.75">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
+    </row>
+    <row r="8" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30.75">
-      <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30.75">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A10" s="33" t="s">
+        <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30.75">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A11" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="27" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A12" s="33" t="s">
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30.75">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30.75">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A13" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="17" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A14" s="34" t="s">
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30.75">
-      <c r="A15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30.75">
-      <c r="A16" s="3" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A15" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A16" s="34" t="s">
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30.75">
-      <c r="A17" s="3" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A17" s="34" t="s">
+        <v>49</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30.75">
-      <c r="A18" s="3" t="s">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A18" s="34" t="s">
+        <v>52</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="24" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A19" s="34" t="s">
+        <v>55</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30.75">
-      <c r="A20" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A20" s="34" t="s">
+        <v>58</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30.75">
-      <c r="A21" s="3" t="s">
-        <v>10</v>
+        <v>59</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A21" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A22" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="14"/>
+    </row>
+    <row r="24" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="14"/>
+    </row>
+    <row r="25" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="14"/>
+    </row>
+    <row r="26" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A26" s="17"/>
+    </row>
+    <row r="27" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A27" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1304,437 +2469,1565 @@
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Public</oddFooter>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8187F376-22C9-4E14-9441-9396C4798D74}">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I62"/>
+  <sheetFormatPr defaultRowHeight="35.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.140625" customWidth="1"/>
-    <col min="6" max="6" width="40.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" customWidth="1"/>
+    <col min="7" max="7" width="35.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="1" spans="1:9" ht="35.25" customHeight="1">
+      <c r="B1" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" s="14" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B2" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="D2" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="E2" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="F2" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="G2" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H2" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="I2" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
+      <c r="A3" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B3" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="C3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="D3" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="F3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="G3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
+      <c r="A4" s="48"/>
+      <c r="B4" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="10" t="s">
+      <c r="C4" s="10" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="16" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="3" t="s">
+      <c r="E4" s="10" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="3" t="s">
+      <c r="F4" s="10" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="3" t="s">
+      <c r="G4" s="10" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="3" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="27"/>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
+      <c r="A5" s="48"/>
+      <c r="B5" s="22" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="3" t="s">
+      <c r="C5" s="10" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="3" t="s">
+      <c r="D5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="3" t="s">
+      <c r="F5" s="10" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="3" t="s">
+      <c r="G5" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="27"/>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
+      <c r="A6" s="48"/>
+      <c r="B6" s="23" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="3" t="s">
+      <c r="C6" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="3" t="s">
+      <c r="D6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="3" t="s">
+      <c r="F6" s="10" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="3" t="s">
+      <c r="G6" s="10" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="3" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="27"/>
+    </row>
+    <row r="7" spans="1:9" ht="39.75" customHeight="1">
+      <c r="A7" s="49"/>
+      <c r="B7" s="22" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="3" t="s">
+      <c r="C7" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="3" t="s">
+      <c r="D7" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="3" t="s">
+      <c r="F7" s="11" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" s="8" customFormat="1">
-      <c r="A26" s="3" t="s">
+      <c r="G7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A8" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="3" t="s">
+      <c r="B8" s="24" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="3" t="s">
+      <c r="C8" s="10" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="3" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="3" t="s">
+      <c r="F8" s="10" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="3" t="s">
+      <c r="G8" s="10" t="s">
         <v>109</v>
       </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="27"/>
+    </row>
+    <row r="9" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="27"/>
+    </row>
+    <row r="10" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="27"/>
+    </row>
+    <row r="11" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="27"/>
+    </row>
+    <row r="12" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A12" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="27"/>
+    </row>
+    <row r="13" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A13" s="48"/>
+      <c r="B13" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="27"/>
+    </row>
+    <row r="14" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A14" s="48"/>
+      <c r="B14" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="27"/>
+    </row>
+    <row r="15" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A15" s="49"/>
+      <c r="B15" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="27"/>
+    </row>
+    <row r="16" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A16" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="27"/>
+    </row>
+    <row r="17" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A17" s="49"/>
+      <c r="B17" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A18" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="27"/>
+    </row>
+    <row r="19" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A19" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="27"/>
+    </row>
+    <row r="20" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A20" s="49"/>
+      <c r="B20" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="27"/>
+    </row>
+    <row r="21" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A21" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="27"/>
+    </row>
+    <row r="22" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A22" s="48"/>
+      <c r="B22" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="27"/>
+    </row>
+    <row r="23" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A23" s="48"/>
+      <c r="B23" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="28"/>
+    </row>
+    <row r="24" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A24" s="49"/>
+      <c r="B24" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="27"/>
+    </row>
+    <row r="25" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A25" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="27"/>
+    </row>
+    <row r="26" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A26" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="28"/>
+    </row>
+    <row r="27" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A27" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="27"/>
+    </row>
+    <row r="28" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A28" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="29"/>
+    </row>
+    <row r="29" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A29" s="49"/>
+      <c r="B29" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A30" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="27"/>
+    </row>
+    <row r="31" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A31" s="46"/>
+      <c r="B31" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="27"/>
+    </row>
+    <row r="32" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A32" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="27"/>
+    </row>
+    <row r="33" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A33" s="45"/>
+      <c r="B33" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="27"/>
+    </row>
+    <row r="34" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A34" s="45"/>
+      <c r="B34" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="27"/>
+    </row>
+    <row r="35" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A35" s="45"/>
+      <c r="B35" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="27"/>
+    </row>
+    <row r="36" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A36" s="45"/>
+      <c r="B36" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="27"/>
+    </row>
+    <row r="37" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A37" s="45"/>
+      <c r="B37" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="27"/>
+    </row>
+    <row r="38" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A38" s="45"/>
+      <c r="B38" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="27"/>
+    </row>
+    <row r="39" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A39" s="46"/>
+      <c r="B39" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="27"/>
+    </row>
+    <row r="40" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A40" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A41" s="45"/>
+      <c r="B41" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="27"/>
+    </row>
+    <row r="42" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A42" s="45"/>
+      <c r="B42" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="27"/>
+    </row>
+    <row r="43" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A43" s="46"/>
+      <c r="B43" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="27"/>
+    </row>
+    <row r="44" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A44" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="27"/>
+    </row>
+    <row r="45" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A45" s="45"/>
+      <c r="B45" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="27"/>
+    </row>
+    <row r="46" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A46" s="45"/>
+      <c r="B46" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="27"/>
+    </row>
+    <row r="47" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A47" s="45"/>
+      <c r="B47" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="27"/>
+    </row>
+    <row r="48" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A48" s="45"/>
+      <c r="B48" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="27"/>
+    </row>
+    <row r="49" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A49" s="46"/>
+      <c r="B49" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A50" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A51" s="45"/>
+      <c r="B51" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A52" s="46"/>
+      <c r="B52" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="27"/>
+    </row>
+    <row r="53" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A53" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="27"/>
+    </row>
+    <row r="54" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A54" s="45"/>
+      <c r="B54" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="27"/>
+    </row>
+    <row r="55" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A55" s="46"/>
+      <c r="B55" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="27"/>
+    </row>
+    <row r="56" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A56" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="27"/>
+    </row>
+    <row r="57" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A57" s="45"/>
+      <c r="B57" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="27"/>
+    </row>
+    <row r="58" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A58" s="46"/>
+      <c r="B58" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="27"/>
+    </row>
+    <row r="59" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A59" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="27"/>
+    </row>
+    <row r="60" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A60" s="45"/>
+      <c r="B60" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="27"/>
+    </row>
+    <row r="61" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A61" s="46"/>
+      <c r="B61" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="28"/>
+    </row>
+    <row r="62" spans="1:9" s="2" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A62" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <autoFilter ref="A2:A62" xr:uid="{8187F376-22C9-4E14-9441-9396C4798D74}"/>
+  <mergeCells count="16">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A39"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2" xr:uid="{CBA1D58F-6A0B-49F5-B5B8-1AF85613F98B}">
-      <formula1>"PASS,FAIL"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35697644-06C4-4BF4-833F-2719491F902D}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="57" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="57" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="57" customWidth="1"/>
+    <col min="4" max="4" width="16" style="57" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="57" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="57" customWidth="1"/>
+    <col min="7" max="7" width="19" style="57" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="57" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="57" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="57" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="56" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>313</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>315</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>316</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE280182-BA0C-4214-9DDE-FF3FDA9A628F}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="24.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="21" customFormat="1">
-      <c r="A1" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" t="s">
-        <v>122</v>
+    <row r="1" spans="1:4" s="3" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -18,7 +18,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="360">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1047,12 +1047,103 @@
   </si>
   <si>
     <t>LOCKED_USER</t>
+  </si>
+  <si>
+    <t>$29.99</t>
+  </si>
+  <si>
+    <t>carry.allTheThings() with the sleek, streamlined Sly Pack that melds uncompromising style with unequaled laptop and tablet protection.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/sauce-backpack-1200x1500.0a0b85a385945026062b.jpg</t>
+  </si>
+  <si>
+    <t>01-07-2026 15:38:47</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>Sauce Labs Bike Light</t>
+  </si>
+  <si>
+    <t>$9.99</t>
+  </si>
+  <si>
+    <t>A red light isn't the desired state in testing but it sure helps when riding your bike at night. Water-resistant with 3 lighting modes, 1 AAA battery included.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/bike-light-1200x1500.37c843b09a7d77409d63.jpg</t>
+  </si>
+  <si>
+    <t>Sauce Labs Bolt T-Shirt</t>
+  </si>
+  <si>
+    <t>$15.99</t>
+  </si>
+  <si>
+    <t>Get your testing superhero on with the Sauce Labs bolt T-shirt. From American Apparel, 100% ringspun combed cotton, heather gray with red bolt.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/bolt-shirt-1200x1500.c2599ac5f0a35ed5931e.jpg</t>
+  </si>
+  <si>
+    <t>Sauce Labs Fleece Jacket</t>
+  </si>
+  <si>
+    <t>$49.99</t>
+  </si>
+  <si>
+    <t>It's not every day that you come across a midweight quarter-zip fleece jacket capable of handling everything from a relaxing day outdoors to a busy day at the office.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/sauce-pullover-1200x1500.51d7ffaf301e698772c8.jpg</t>
+  </si>
+  <si>
+    <t>Sauce Labs Onesie</t>
+  </si>
+  <si>
+    <t>$7.99</t>
+  </si>
+  <si>
+    <t>Rib snap infant onesie for the junior automation engineer in development. Reinforced 3-snap bottom closure, two-needle hemmed sleeved and bottom won't unravel.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/red-onesie-1200x1500.2ec615b271ef4c3bc430.jpg</t>
+  </si>
+  <si>
+    <t>Test.allTheThings() T-Shirt (Red)</t>
+  </si>
+  <si>
+    <t>This classic Sauce Labs t-shirt is perfect to wear when cozying up to your keyboard to automate a few tests. Super-soft and comfy ringspun combed cotton.</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/static/media/red-tatt-1200x1500.30dadef477804e54fc7b.jpg</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack - $29.99</t>
+  </si>
+  <si>
+    <t>Sauce Labs Bike Light - $9.99</t>
+  </si>
+  <si>
+    <t>Sauce Labs Bolt T-Shirt - $15.99</t>
+  </si>
+  <si>
+    <t>Sauce Labs Fleece Jacket - $49.99</t>
+  </si>
+  <si>
+    <t>Sauce Labs Onesie - $7.99</t>
+  </si>
+  <si>
+    <t>Test.allTheThings() T-Shirt (Red) - $15.99</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -2134,11 +2225,11 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="35.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="16.5703125"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.140625"/>
+    <col min="3" max="3" customWidth="true" style="2" width="50.0"/>
+    <col min="4" max="4" customWidth="true" style="1" width="18.0"/>
+    <col min="5" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.25" customHeight="1">
@@ -2481,15 +2572,15 @@
   <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="35.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" style="43" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" customWidth="1"/>
-    <col min="7" max="7" width="35.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="43" width="20.28515625"/>
+    <col min="2" max="2" customWidth="true" style="6" width="19.5703125"/>
+    <col min="3" max="3" customWidth="true" width="28.140625"/>
+    <col min="4" max="4" customWidth="true" width="20.7109375"/>
+    <col min="5" max="5" customWidth="true" width="29.0"/>
+    <col min="6" max="6" customWidth="true" width="32.5703125"/>
+    <col min="7" max="7" customWidth="true" width="35.28515625"/>
+    <col min="8" max="8" customWidth="true" width="18.7109375"/>
+    <col min="9" max="9" customWidth="true" width="23.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="35.25" customHeight="1">
@@ -3886,20 +3977,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35697644-06C4-4BF4-833F-2719491F902D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="57" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="57" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="57" customWidth="1"/>
-    <col min="4" max="4" width="16" style="57" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="57" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="57" customWidth="1"/>
-    <col min="7" max="7" width="19" style="57" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="57" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="57" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="57" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="17.42578125"/>
+    <col min="2" max="2" customWidth="true" style="57" width="18.5703125"/>
+    <col min="3" max="3" customWidth="true" style="57" width="17.42578125"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.0"/>
+    <col min="5" max="5" customWidth="true" style="57" width="19.28515625"/>
+    <col min="6" max="6" customWidth="true" style="57" width="18.7109375"/>
+    <col min="7" max="7" customWidth="true" style="57" width="19.0"/>
+    <col min="8" max="8" customWidth="true" style="57" width="18.5703125"/>
+    <col min="9" max="9" customWidth="true" style="57" width="14.42578125"/>
+    <col min="10" max="10" customWidth="true" style="57" width="12.42578125"/>
+    <col min="11" max="16384" style="57" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="56" customFormat="1" ht="30" customHeight="1">
@@ -3932,6 +4023,198 @@
       </c>
       <c r="J1" s="56" t="s">
         <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="57">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="57">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s" s="57">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s" s="57">
+        <v>332</v>
+      </c>
+      <c r="E2" t="s" s="57">
+        <v>354</v>
+      </c>
+      <c r="F2" t="s" s="57">
+        <v>359</v>
+      </c>
+      <c r="G2" t="s" s="57">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s" s="57">
+        <v>357</v>
+      </c>
+      <c r="I2" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J2" t="s" s="57">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="57">
+        <v>335</v>
+      </c>
+      <c r="B3" t="s" s="57">
+        <v>336</v>
+      </c>
+      <c r="C3" t="s" s="57">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s" s="57">
+        <v>338</v>
+      </c>
+      <c r="E3" t="s" s="57">
+        <v>355</v>
+      </c>
+      <c r="F3" t="s" s="57">
+        <v>358</v>
+      </c>
+      <c r="G3" t="s" s="57">
+        <v>355</v>
+      </c>
+      <c r="H3" t="s" s="57">
+        <v>354</v>
+      </c>
+      <c r="I3" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J3" t="s" s="57">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="57">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s" s="57">
+        <v>340</v>
+      </c>
+      <c r="C4" t="s" s="57">
+        <v>341</v>
+      </c>
+      <c r="D4" t="s" s="57">
+        <v>342</v>
+      </c>
+      <c r="E4" t="s" s="57">
+        <v>356</v>
+      </c>
+      <c r="F4" t="s" s="57">
+        <v>357</v>
+      </c>
+      <c r="G4" t="s" s="57">
+        <v>356</v>
+      </c>
+      <c r="H4" t="s" s="57">
+        <v>356</v>
+      </c>
+      <c r="I4" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J4" t="s" s="57">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="57">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s" s="57">
+        <v>344</v>
+      </c>
+      <c r="C5" t="s" s="57">
+        <v>345</v>
+      </c>
+      <c r="D5" t="s" s="57">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s" s="57">
+        <v>357</v>
+      </c>
+      <c r="F5" t="s" s="57">
+        <v>356</v>
+      </c>
+      <c r="G5" t="s" s="57">
+        <v>359</v>
+      </c>
+      <c r="H5" t="s" s="57">
+        <v>359</v>
+      </c>
+      <c r="I5" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J5" t="s" s="57">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="57">
+        <v>347</v>
+      </c>
+      <c r="B6" t="s" s="57">
+        <v>348</v>
+      </c>
+      <c r="C6" t="s" s="57">
+        <v>349</v>
+      </c>
+      <c r="D6" t="s" s="57">
+        <v>350</v>
+      </c>
+      <c r="E6" t="s" s="57">
+        <v>358</v>
+      </c>
+      <c r="F6" t="s" s="57">
+        <v>355</v>
+      </c>
+      <c r="G6" t="s" s="57">
+        <v>354</v>
+      </c>
+      <c r="H6" t="s" s="57">
+        <v>355</v>
+      </c>
+      <c r="I6" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J6" t="s" s="57">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="57">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s" s="57">
+        <v>340</v>
+      </c>
+      <c r="C7" t="s" s="57">
+        <v>352</v>
+      </c>
+      <c r="D7" t="s" s="57">
+        <v>353</v>
+      </c>
+      <c r="E7" t="s" s="57">
+        <v>359</v>
+      </c>
+      <c r="F7" t="s" s="57">
+        <v>354</v>
+      </c>
+      <c r="G7" t="s" s="57">
+        <v>357</v>
+      </c>
+      <c r="H7" t="s" s="57">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s" s="57">
+        <v>333</v>
+      </c>
+      <c r="J7" t="s" s="57">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3944,10 +4227,10 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="11.5703125"/>
+    <col min="2" max="2" customWidth="true" width="18.0"/>
+    <col min="3" max="3" customWidth="true" width="16.140625"/>
+    <col min="4" max="4" customWidth="true" width="22.5703125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" ht="24.75" customHeight="1">

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -10,8 +10,8 @@
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
-    <sheet name="Inventory" sheetId="4" r:id="rId3"/>
     <sheet name="Login" sheetId="3" r:id="rId4"/>
+    <sheet name="Inventory" r:id="rId8" sheetId="5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="362">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1137,6 +1137,12 @@
   </si>
   <si>
     <t>Test.allTheThings() T-Shirt (Red) - $15.99</t>
+  </si>
+  <si>
+    <t>02-07-2026 11:48:18</t>
+  </si>
+  <si>
+    <t>02-07-2026 11:50:56</t>
   </si>
 </sst>
 </file>
@@ -3975,253 +3981,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35697644-06C4-4BF4-833F-2719491F902D}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="17.42578125"/>
-    <col min="2" max="2" customWidth="true" style="57" width="18.5703125"/>
-    <col min="3" max="3" customWidth="true" style="57" width="17.42578125"/>
-    <col min="4" max="4" customWidth="true" style="57" width="16.0"/>
-    <col min="5" max="5" customWidth="true" style="57" width="19.28515625"/>
-    <col min="6" max="6" customWidth="true" style="57" width="18.7109375"/>
-    <col min="7" max="7" customWidth="true" style="57" width="19.0"/>
-    <col min="8" max="8" customWidth="true" style="57" width="18.5703125"/>
-    <col min="9" max="9" customWidth="true" style="57" width="14.42578125"/>
-    <col min="10" max="10" customWidth="true" style="57" width="12.42578125"/>
-    <col min="11" max="16384" style="57" width="9.140625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="56" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>309</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>310</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>311</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>312</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>313</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>314</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>315</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>316</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="57">
-        <v>191</v>
-      </c>
-      <c r="B2" t="s" s="57">
-        <v>330</v>
-      </c>
-      <c r="C2" t="s" s="57">
-        <v>331</v>
-      </c>
-      <c r="D2" t="s" s="57">
-        <v>332</v>
-      </c>
-      <c r="E2" t="s" s="57">
-        <v>354</v>
-      </c>
-      <c r="F2" t="s" s="57">
-        <v>359</v>
-      </c>
-      <c r="G2" t="s" s="57">
-        <v>358</v>
-      </c>
-      <c r="H2" t="s" s="57">
-        <v>357</v>
-      </c>
-      <c r="I2" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J2" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="57">
-        <v>335</v>
-      </c>
-      <c r="B3" t="s" s="57">
-        <v>336</v>
-      </c>
-      <c r="C3" t="s" s="57">
-        <v>337</v>
-      </c>
-      <c r="D3" t="s" s="57">
-        <v>338</v>
-      </c>
-      <c r="E3" t="s" s="57">
-        <v>355</v>
-      </c>
-      <c r="F3" t="s" s="57">
-        <v>358</v>
-      </c>
-      <c r="G3" t="s" s="57">
-        <v>355</v>
-      </c>
-      <c r="H3" t="s" s="57">
-        <v>354</v>
-      </c>
-      <c r="I3" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J3" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="57">
-        <v>339</v>
-      </c>
-      <c r="B4" t="s" s="57">
-        <v>340</v>
-      </c>
-      <c r="C4" t="s" s="57">
-        <v>341</v>
-      </c>
-      <c r="D4" t="s" s="57">
-        <v>342</v>
-      </c>
-      <c r="E4" t="s" s="57">
-        <v>356</v>
-      </c>
-      <c r="F4" t="s" s="57">
-        <v>357</v>
-      </c>
-      <c r="G4" t="s" s="57">
-        <v>356</v>
-      </c>
-      <c r="H4" t="s" s="57">
-        <v>356</v>
-      </c>
-      <c r="I4" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J4" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="57">
-        <v>343</v>
-      </c>
-      <c r="B5" t="s" s="57">
-        <v>344</v>
-      </c>
-      <c r="C5" t="s" s="57">
-        <v>345</v>
-      </c>
-      <c r="D5" t="s" s="57">
-        <v>346</v>
-      </c>
-      <c r="E5" t="s" s="57">
-        <v>357</v>
-      </c>
-      <c r="F5" t="s" s="57">
-        <v>356</v>
-      </c>
-      <c r="G5" t="s" s="57">
-        <v>359</v>
-      </c>
-      <c r="H5" t="s" s="57">
-        <v>359</v>
-      </c>
-      <c r="I5" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J5" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="57">
-        <v>347</v>
-      </c>
-      <c r="B6" t="s" s="57">
-        <v>348</v>
-      </c>
-      <c r="C6" t="s" s="57">
-        <v>349</v>
-      </c>
-      <c r="D6" t="s" s="57">
-        <v>350</v>
-      </c>
-      <c r="E6" t="s" s="57">
-        <v>358</v>
-      </c>
-      <c r="F6" t="s" s="57">
-        <v>355</v>
-      </c>
-      <c r="G6" t="s" s="57">
-        <v>354</v>
-      </c>
-      <c r="H6" t="s" s="57">
-        <v>355</v>
-      </c>
-      <c r="I6" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J6" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="57">
-        <v>351</v>
-      </c>
-      <c r="B7" t="s" s="57">
-        <v>340</v>
-      </c>
-      <c r="C7" t="s" s="57">
-        <v>352</v>
-      </c>
-      <c r="D7" t="s" s="57">
-        <v>353</v>
-      </c>
-      <c r="E7" t="s" s="57">
-        <v>359</v>
-      </c>
-      <c r="F7" t="s" s="57">
-        <v>354</v>
-      </c>
-      <c r="G7" t="s" s="57">
-        <v>357</v>
-      </c>
-      <c r="H7" t="s" s="57">
-        <v>358</v>
-      </c>
-      <c r="I7" t="s" s="57">
-        <v>333</v>
-      </c>
-      <c r="J7" t="s" s="57">
-        <v>334</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE280182-BA0C-4214-9DDE-FF3FDA9A628F}">
   <dimension ref="A1:D6"/>
@@ -4316,4 +4075,238 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="363">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1143,6 +1143,9 @@
   </si>
   <si>
     <t>02-07-2026 11:50:56</t>
+  </si>
+  <si>
+    <t>02-07-2026 13:37:54</t>
   </si>
 </sst>
 </file>
@@ -4140,7 +4143,7 @@
         <v>357</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>334</v>
@@ -4172,7 +4175,7 @@
         <v>354</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>334</v>
@@ -4204,7 +4207,7 @@
         <v>356</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>334</v>
@@ -4236,7 +4239,7 @@
         <v>359</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>334</v>
@@ -4268,7 +4271,7 @@
         <v>355</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>334</v>
@@ -4300,7 +4303,7 @@
         <v>358</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>334</v>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId4"/>
     <sheet name="Inventory" r:id="rId8" sheetId="5"/>
+    <sheet name="Logout" r:id="rId9" sheetId="6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="366">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1146,6 +1147,15 @@
   </si>
   <si>
     <t>02-07-2026 13:37:54</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>05-07-2026 13:13:57</t>
   </si>
 </sst>
 </file>
@@ -4312,4 +4322,42 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Login" sheetId="3" r:id="rId4"/>
     <sheet name="Inventory" r:id="rId8" sheetId="5"/>
     <sheet name="Logout" r:id="rId9" sheetId="6"/>
+    <sheet name="UIValidation" r:id="rId10" sheetId="7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="396">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1156,6 +1157,96 @@
   </si>
   <si>
     <t>05-07-2026 13:13:57</t>
+  </si>
+  <si>
+    <t>Login Button Alignment</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:42:44</t>
+  </si>
+  <si>
+    <t>Inventory Layout</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:42:49</t>
+  </si>
+  <si>
+    <t>Cart Icon</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:42:53</t>
+  </si>
+  <si>
+    <t>Footer Links</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:42:58</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:52:49</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:52:53</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:52:57</t>
+  </si>
+  <si>
+    <t>09-07-2026 06:53:02</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:12:37</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:12:45</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:12:49</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:16:43</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:16:47</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:16:51</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:16:55</t>
+  </si>
+  <si>
+    <t>SauceDemo Logo</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:23:56</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:23:58</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:24:01</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:24:04</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:24:07</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:32:31</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:32:36</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:32:38</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:32:41</t>
+  </si>
+  <si>
+    <t>09-07-2026 07:32:43</t>
   </si>
 </sst>
 </file>
@@ -4360,4 +4451,116 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>395</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="401">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1247,6 +1247,21 @@
   </si>
   <si>
     <t>09-07-2026 07:32:43</t>
+  </si>
+  <si>
+    <t>09-07-2026 10:52:12</t>
+  </si>
+  <si>
+    <t>09-07-2026 10:52:20</t>
+  </si>
+  <si>
+    <t>09-07-2026 10:52:26</t>
+  </si>
+  <si>
+    <t>09-07-2026 10:52:34</t>
+  </si>
+  <si>
+    <t>09-07-2026 10:52:39</t>
   </si>
 </sst>
 </file>
@@ -4486,7 +4501,7 @@
         <v>364</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>334</v>
@@ -4503,7 +4518,7 @@
         <v>364</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>334</v>
@@ -4520,7 +4535,7 @@
         <v>364</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>334</v>
@@ -4537,7 +4552,7 @@
         <v>364</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>334</v>
@@ -4554,7 +4569,7 @@
         <v>364</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>334</v>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -11,9 +11,12 @@
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId4"/>
-    <sheet name="Inventory" r:id="rId8" sheetId="5"/>
     <sheet name="Logout" r:id="rId9" sheetId="6"/>
     <sheet name="UIValidation" r:id="rId10" sheetId="7"/>
+    <sheet name="ErrorMessages" r:id="rId11" sheetId="8"/>
+    <sheet name="Cart" r:id="rId13" sheetId="10"/>
+    <sheet name="Checkout" r:id="rId14" sheetId="11"/>
+    <sheet name="Inventory" r:id="rId12" sheetId="12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="485">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1262,6 +1265,258 @@
   </si>
   <si>
     <t>09-07-2026 10:52:39</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Expected Error</t>
+  </si>
+  <si>
+    <t>Actual Error</t>
+  </si>
+  <si>
+    <t>Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:00:33</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:00:39</t>
+  </si>
+  <si>
+    <t>Username is required</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username is required</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:00:44</t>
+  </si>
+  <si>
+    <t>Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>Epic sadface: Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:00:50</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/sauce-backpack-1200x1500-CjRW-Djj.jpg</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:01:30</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/bike-light-1200x1500-DxcZRFOA.jpg</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/bolt-shirt-1200x1500-mR0ldpVS.jpg</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/sauce-pullover-1200x1500-BfbI-PSd.jpg</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/red-onesie-1200x1500-BrSuq0ic.jpg</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/assets/red-tatt-1200x1500-E-qp6aYf.jpg</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Added</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:02:30</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:02:31</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:02:55</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:02:56</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:03:25</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:03:26</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Error Message</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>560001</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Error: First Name is required</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:04:24</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Error: Last Name is required</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:04:30</t>
+  </si>
+  <si>
+    <t>Error: Postal Code is required</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:04:37</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:05:16</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:07:16</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:07:24</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:07:29</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:07:35</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:07:40</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:28</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:29</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:37</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:44</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:52</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:10:59</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:06</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:32</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:37</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:42</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:47</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:11:53</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:12:44</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:12:49</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:12:53</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:12:59</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:13:04</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:17:26</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:17:32</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:17:37</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:17:42</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:19:57</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:21:15</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:22:14</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:24:21</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:24:27</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:24:34</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:25:33</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:26:41</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:26:49</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:26:55</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:27:00</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:27:06</t>
   </si>
 </sst>
 </file>
@@ -2691,6 +2946,398 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>422</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>431</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>433</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B2" s="0"/>
+      <c r="C2" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>476</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D4" s="0"/>
+      <c r="E4" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>443</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>478</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>414</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>417</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>418</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>420</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8187F376-22C9-4E14-9441-9396C4798D74}">
   <sheetPr filterMode="1"/>
@@ -4196,240 +4843,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>309</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>311</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>313</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>331</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>332</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>335</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>336</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>337</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>338</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>339</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>341</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>342</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="I4" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>343</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>344</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>345</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>346</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>347</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>348</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>349</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>350</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="I6" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>351</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>352</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>353</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="I7" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D2"/>
@@ -4457,7 +4870,7 @@
         <v>364</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>365</v>
+        <v>479</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>334</v>
@@ -4470,7 +4883,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4575,6 +4988,386 @@
         <v>334</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>446</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>447</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>449</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>481</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>482</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>484</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>401</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>470</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>471</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>472</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Cart" r:id="rId13" sheetId="10"/>
     <sheet name="Checkout" r:id="rId14" sheetId="11"/>
     <sheet name="Inventory" r:id="rId12" sheetId="12"/>
+    <sheet name="SessionManagement" r:id="rId15" sheetId="13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="492">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1517,6 +1518,27 @@
   </si>
   <si>
     <t>09-07-2026 14:27:06</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:50:39</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:50:47</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:50:54</t>
+  </si>
+  <si>
+    <t>09-07-2026 14:51:05</t>
+  </si>
+  <si>
+    <t>09-07-2026 15:13:47</t>
+  </si>
+  <si>
+    <t>09-07-2026 15:13:56</t>
+  </si>
+  <si>
+    <t>09-07-2026 15:14:07</t>
   </si>
 </sst>
 </file>
@@ -3338,6 +3360,67 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>491</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8187F376-22C9-4E14-9441-9396C4798D74}">
   <sheetPr filterMode="1"/>
@@ -5293,7 +5376,7 @@
         <v>364</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>334</v>
@@ -5316,7 +5399,7 @@
         <v>364</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>334</v>
@@ -5339,7 +5422,7 @@
         <v>364</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>334</v>
@@ -5362,7 +5445,7 @@
         <v>364</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>334</v>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -16,8 +16,8 @@
     <sheet name="ErrorMessages" r:id="rId11" sheetId="8"/>
     <sheet name="Cart" r:id="rId13" sheetId="10"/>
     <sheet name="Checkout" r:id="rId14" sheetId="11"/>
-    <sheet name="Inventory" r:id="rId12" sheetId="12"/>
     <sheet name="SessionManagement" r:id="rId15" sheetId="13"/>
+    <sheet name="Inventory" r:id="rId16" sheetId="14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="560">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1539,6 +1539,210 @@
   </si>
   <si>
     <t>09-07-2026 15:14:07</t>
+  </si>
+  <si>
+    <t>09-07-2026 16:41:41</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:36:58</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:37:04</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:37:09</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:37:14</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:37:19</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:40:44</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:40:51</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:40:57</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:41:03</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:41:09</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:47:20</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:47:21</t>
+  </si>
+  <si>
+    <t>Removed</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:03</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:10</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:37</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:43</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:49</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:48:56</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:49:02</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:24</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:30</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:36</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:41</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:46</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:51</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:50:56</t>
+  </si>
+  <si>
+    <t>10-07-2026 10:51:02</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:05</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:11</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:19</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:26</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:33</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:50</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:15:51</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:16:15</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:16:20</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:16:26</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:16:32</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:21</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:26</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:31</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:36</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:41</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:17:55</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:18:00</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:18:07</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:25:17</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:25:23</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:25:31</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:25:38</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:25:48</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:06</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:07</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:14</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:20</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:25</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:31</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:26:38</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:27:26</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:27:32</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:27:37</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:27:42</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:27:47</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:28:01</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:28:06</t>
+  </si>
+  <si>
+    <t>10-07-2026 11:28:11</t>
   </si>
 </sst>
 </file>
@@ -2970,7 +3174,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2991,26 +3195,6 @@
       </c>
       <c r="F1" t="s" s="0">
         <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>475</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3020,7 +3204,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3049,84 +3233,226 @@
         <v>317</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="B2" s="0"/>
-      <c r="C2" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>438</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>476</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C3" s="0"/>
-      <c r="D3" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>477</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>169</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D4" s="0"/>
-      <c r="E4" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>443</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>478</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>491</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>538</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>539</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -3189,7 +3515,7 @@
         <v>357</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>334</v>
@@ -3221,7 +3547,7 @@
         <v>354</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>334</v>
@@ -3253,7 +3579,7 @@
         <v>356</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>334</v>
@@ -3285,7 +3611,7 @@
         <v>359</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>334</v>
@@ -3317,7 +3643,7 @@
         <v>355</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>334</v>
@@ -3349,70 +3675,9 @@
         <v>358</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>489</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>490</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>491</v>
-      </c>
-      <c r="E3" t="s" s="0">
         <v>334</v>
       </c>
     </row>
@@ -4928,7 +5193,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4943,20 +5208,6 @@
       </c>
       <c r="D1" t="s" s="0">
         <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>180</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>479</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4966,7 +5217,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4984,346 +5235,6 @@
       </c>
       <c r="E1" t="s" s="0">
         <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>396</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>397</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>399</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>446</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>447</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>448</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>449</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>450</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>464</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>466</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>467</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>468</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>480</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>481</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>482</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>483</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>484</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5333,7 +5244,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5359,98 +5270,6 @@
         <v>317</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>485</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>486</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>409</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>487</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>411</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>412</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>488</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="667">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -1743,6 +1743,327 @@
   </si>
   <si>
     <t>10-07-2026 11:28:11</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:32:05</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:32:12</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:32:18</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:32:27</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:12</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:18</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:23</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:30</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:37</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:57</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:46:58</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:47:06</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:47:13</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:47:20</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:47:27</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:47:33</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:48:26</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:48:31</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:48:36</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:48:41</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:48:47</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:49:03</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:49:09</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:49:15</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:05:43</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:06:54</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:06:55</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:08:13</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:08:14</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:12:56</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:13:03</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:13:10</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:13:17</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:14:02</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:14:09</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:14:15</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:14:21</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:20:07</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:20:14</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:20:15</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:20:24</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:20:34</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:33:47</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:33:48</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:33:57</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:34:06</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:34:15</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:45:58</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:05</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:09</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:11</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:17</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:18</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:46:24</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:57:33</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:57:42</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:57:49</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:57:52</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:57:56</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:58:10</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:06</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:11</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:14</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:21</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:24</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:30</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:34</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:37</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:46</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:54:51</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:14</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:15</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:16</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:24</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:25</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:27</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:38</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:55:50</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:56:01</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:56:02</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:56:13</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:56:27</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:57:38</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:57:46</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:57:54</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:03</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:10</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:12</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:19</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:29</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:33</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:39</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:58:44</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:59:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:59:07</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:59:13</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:59:20</t>
+  </si>
+  <si>
+    <t>11-07-2026 15:36:45</t>
+  </si>
+  <si>
+    <t>11-07-2026 15:36:46</t>
+  </si>
+  <si>
+    <t>11-07-2026 15:47:56</t>
+  </si>
+  <si>
+    <t>11-07-2026 15:47:57</t>
+  </si>
+  <si>
+    <t>11-07-2026 15:54:11</t>
+  </si>
+  <si>
+    <t>11-07-2026 16:00:37</t>
+  </si>
+  <si>
+    <t>11-07-2026 16:00:38</t>
+  </si>
+  <si>
+    <t>11-07-2026 17:08:28</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +2071,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,8 +2125,53 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1818,8 +2184,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1996,11 +2372,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2170,6 +2564,57 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="true" vertical="center" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="true" vertical="center" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3174,7 +3619,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3195,6 +3640,166 @@
       </c>
       <c r="F1" t="s" s="0">
         <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>631</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>632</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>632</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>633</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>634</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3809,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3836,202 @@
       </c>
       <c r="H1" t="s" s="0">
         <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>453</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>636</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>453</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>637</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B4" s="0"/>
+      <c r="C4" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>637</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>638</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B6" s="0"/>
+      <c r="C6" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>638</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>639</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D8" s="0"/>
+      <c r="E8" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>443</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>640</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="D9" s="0"/>
+      <c r="E9" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>443</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>641</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3240,7 +4041,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3444,6 +4245,159 @@
         <v>559</v>
       </c>
       <c r="E12" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>582</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>583</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>652</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>654</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>655</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>656</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>657</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>658</v>
+      </c>
+      <c r="E21" t="s" s="0">
         <v>334</v>
       </c>
     </row>
@@ -3456,50 +4410,62 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="30.0"/>
+    <col min="2" max="2" customWidth="true" width="12.0"/>
+    <col min="3" max="3" customWidth="true" width="80.0"/>
+    <col min="4" max="4" customWidth="true" width="40.0"/>
+    <col min="5" max="5" customWidth="true" width="35.0"/>
+    <col min="6" max="6" customWidth="true" width="35.0"/>
+    <col min="7" max="7" customWidth="true" width="35.0"/>
+    <col min="8" max="8" customWidth="true" width="35.0"/>
+    <col min="9" max="9" customWidth="true" width="25.0"/>
+    <col min="10" max="10" customWidth="true" width="12.0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="72">
         <v>309</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s" s="72">
         <v>310</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s" s="72">
         <v>3</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s" s="72">
         <v>311</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s" s="72">
         <v>312</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s" s="72">
         <v>313</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s" s="72">
         <v>131</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s" s="72">
         <v>135</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s" s="72">
         <v>316</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s" s="72">
         <v>317</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" ht="30.0" customHeight="true">
+      <c r="A2" t="s" s="74">
         <v>191</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s" s="74">
         <v>330</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s" s="74">
         <v>331</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s" s="74">
         <v>414</v>
       </c>
       <c r="E2" t="s" s="0">
@@ -3514,24 +4480,24 @@
       <c r="H2" t="s" s="0">
         <v>357</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J2" t="s" s="0">
+      <c r="I2" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J2" t="s" s="74">
         <v>334</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" ht="30.0" customHeight="true">
+      <c r="A3" t="s" s="74">
         <v>335</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s" s="74">
         <v>336</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s" s="74">
         <v>337</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s" s="74">
         <v>416</v>
       </c>
       <c r="E3" t="s" s="0">
@@ -3546,24 +4512,24 @@
       <c r="H3" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="I3" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J3" t="s" s="0">
+      <c r="I3" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J3" t="s" s="74">
         <v>334</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" ht="30.0" customHeight="true">
+      <c r="A4" t="s" s="74">
         <v>339</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s" s="74">
         <v>340</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s" s="74">
         <v>341</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s" s="74">
         <v>417</v>
       </c>
       <c r="E4" t="s" s="0">
@@ -3578,24 +4544,24 @@
       <c r="H4" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="I4" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J4" t="s" s="0">
+      <c r="I4" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J4" t="s" s="74">
         <v>334</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
+    <row r="5" ht="30.0" customHeight="true">
+      <c r="A5" t="s" s="74">
         <v>343</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s" s="74">
         <v>344</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s" s="74">
         <v>345</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s" s="74">
         <v>418</v>
       </c>
       <c r="E5" t="s" s="0">
@@ -3610,24 +4576,24 @@
       <c r="H5" t="s" s="0">
         <v>359</v>
       </c>
-      <c r="I5" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J5" t="s" s="0">
+      <c r="I5" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J5" t="s" s="74">
         <v>334</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
+    <row r="6" ht="30.0" customHeight="true">
+      <c r="A6" t="s" s="74">
         <v>347</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s" s="74">
         <v>348</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s" s="74">
         <v>349</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s" s="74">
         <v>419</v>
       </c>
       <c r="E6" t="s" s="0">
@@ -3642,24 +4608,24 @@
       <c r="H6" t="s" s="0">
         <v>355</v>
       </c>
-      <c r="I6" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J6" t="s" s="0">
+      <c r="I6" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J6" t="s" s="74">
         <v>334</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
+    <row r="7" ht="30.0" customHeight="true">
+      <c r="A7" t="s" s="74">
         <v>351</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s" s="74">
         <v>340</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="C7" t="s" s="74">
         <v>352</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s" s="74">
         <v>420</v>
       </c>
       <c r="E7" t="s" s="0">
@@ -3674,10 +4640,10 @@
       <c r="H7" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="I7" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J7" t="s" s="0">
+      <c r="I7" t="s" s="74">
+        <v>666</v>
+      </c>
+      <c r="J7" t="s" s="74">
         <v>334</v>
       </c>
     </row>
@@ -5193,7 +6159,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5208,6 +6174,20 @@
       </c>
       <c r="D1" t="s" s="0">
         <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>642</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5217,7 +6197,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5235,6 +6215,176 @@
       </c>
       <c r="E1" t="s" s="0">
         <v>317</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>643</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>644</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>645</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>647</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>648</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>649</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>650</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>651</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>653</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5244,7 +6394,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5270,6 +6420,190 @@
         <v>317</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>621</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>622</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>623</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>624</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>625</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>626</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>627</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>628</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2626746-586E-403B-87A8-8A146426B7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E10618-ED01-4677-BDDC-034849CC3AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
-    <sheet name="Login" sheetId="3" r:id="rId4"/>
-    <sheet name="Logout" r:id="rId9" sheetId="6"/>
-    <sheet name="UIValidation" r:id="rId10" sheetId="7"/>
-    <sheet name="ErrorMessages" r:id="rId11" sheetId="8"/>
-    <sheet name="Cart" r:id="rId13" sheetId="10"/>
-    <sheet name="Checkout" r:id="rId14" sheetId="11"/>
-    <sheet name="SessionManagement" r:id="rId15" sheetId="13"/>
-    <sheet name="Inventory" r:id="rId16" sheetId="14"/>
+    <sheet name="Login" sheetId="3" r:id="rId3"/>
+    <sheet name="PerformanceComparison" r:id="rId7" sheetId="4"/>
+    <sheet name="ErrorMessages" r:id="rId8" sheetId="5"/>
+    <sheet name="Cart" r:id="rId10" sheetId="7"/>
+    <sheet name="Checkout" r:id="rId11" sheetId="8"/>
+    <sheet name="Logout" r:id="rId12" sheetId="9"/>
+    <sheet name="UIValidation" r:id="rId13" sheetId="10"/>
+    <sheet name="SessionManagement" r:id="rId14" sheetId="11"/>
+    <sheet name="Inventory" r:id="rId15" sheetId="12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$2:$A$62</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="642">
   <si>
     <t>Sauce Demo Test Scenario</t>
   </si>
@@ -346,7 +347,7 @@
     <t>SD_TC_005</t>
   </si>
   <si>
-    <t>Locked out user login</t>
+    <t>Login with locked out user</t>
   </si>
   <si>
     <t>locked_out_user/secret_sauce</t>
@@ -362,7 +363,7 @@
     <t>SD_TC_006</t>
   </si>
   <si>
-    <t>Verify all products displayed</t>
+    <t>Complete Inventory Flow</t>
   </si>
   <si>
     <t>Login successful</t>
@@ -519,7 +520,7 @@
     <t>SD_TC_018</t>
   </si>
   <si>
-    <t>Continue shopping</t>
+    <t>Verify Complete Cart Functionality</t>
   </si>
   <si>
     <t>Click Continue Shopping</t>
@@ -562,7 +563,7 @@
     <t>SD_TC_022</t>
   </si>
   <si>
-    <t>Checkout without zip code</t>
+    <t>Checkout without Postal Code</t>
   </si>
   <si>
     <t>SD_TS_008
@@ -598,6 +599,9 @@
     <t>SD_TC_025</t>
   </si>
   <si>
+    <t>Verify Logout Functionality</t>
+  </si>
+  <si>
     <t>User logged in</t>
   </si>
   <si>
@@ -664,7 +668,7 @@
     <t>SD_TC_031</t>
   </si>
   <si>
-    <t>Verify Remove button on product details</t>
+    <t>Verify Remove button on Product Details page</t>
   </si>
   <si>
     <t>Click Remove</t>
@@ -915,7 +919,7 @@
     <t>SD_TC_054</t>
   </si>
   <si>
-    <t>Verify Login page load time</t>
+    <t>Verify Performance</t>
   </si>
   <si>
     <t>Application launched</t>
@@ -943,7 +947,7 @@
     <t>SD_TC_057</t>
   </si>
   <si>
-    <t>Verify keyboard navigation</t>
+    <t>Verify Accessibility</t>
   </si>
   <si>
     <t>Use Tab key</t>
@@ -992,6 +996,141 @@
     <t>Complete purchase flow</t>
   </si>
   <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>ExceptedResult</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
+    <t>wrong_password</t>
+  </si>
+  <si>
+    <t>INVALID_CREDENTIALS</t>
+  </si>
+  <si>
+    <t>wrong_user</t>
+  </si>
+  <si>
+    <t>USERNAME_REQUIRED</t>
+  </si>
+  <si>
+    <t>LOCKED_USER</t>
+  </si>
+  <si>
+    <t>Chrome (ms)</t>
+  </si>
+  <si>
+    <t>Edge (ms)</t>
+  </si>
+  <si>
+    <t>Faster Browser</t>
+  </si>
+  <si>
+    <t>Difference (ms)</t>
+  </si>
+  <si>
+    <t>Winner %</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Expected Error</t>
+  </si>
+  <si>
+    <t>Actual Error</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Execution Time</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>8.18%</t>
+  </si>
+  <si>
+    <t>Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:42:45</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:42:47</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>17.27%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:42:52</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:42:58</t>
+  </si>
+  <si>
+    <t>30.45%</t>
+  </si>
+  <si>
+    <t>Username is required</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username is required</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:07</t>
+  </si>
+  <si>
+    <t>Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>Epic sadface: Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>14.16%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:15</t>
+  </si>
+  <si>
+    <t>17.70%</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -1007,67 +1146,16 @@
     <t>Z-A</t>
   </si>
   <si>
-    <t>Low - High</t>
-  </si>
-  <si>
-    <t>High - Low</t>
-  </si>
-  <si>
-    <t>Execution Time</t>
-  </si>
-  <si>
-    <t>Browser</t>
-  </si>
-  <si>
-    <t>TC_ID</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>ExceptedResult</t>
-  </si>
-  <si>
-    <t>standard_user</t>
-  </si>
-  <si>
-    <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>SUCCESS</t>
-  </si>
-  <si>
-    <t>wrong_password</t>
-  </si>
-  <si>
-    <t>INVALID_CREDENTIALS</t>
-  </si>
-  <si>
-    <t>wrong_user</t>
-  </si>
-  <si>
-    <t>USERNAME_REQUIRED</t>
-  </si>
-  <si>
-    <t>LOCKED_USER</t>
-  </si>
-  <si>
     <t>$29.99</t>
   </si>
   <si>
     <t>carry.allTheThings() with the sleek, streamlined Sly Pack that melds uncompromising style with unequaled laptop and tablet protection.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/sauce-backpack-1200x1500.0a0b85a385945026062b.jpg</t>
-  </si>
-  <si>
-    <t>01-07-2026 15:38:47</t>
-  </si>
-  <si>
-    <t>chrome</t>
+    <t>https://www.saucedemo.com/assets/sauce-backpack-1200x1500-CjRW-Djj.jpg</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:16</t>
   </si>
   <si>
     <t>Sauce Labs Bike Light</t>
@@ -1079,7 +1167,7 @@
     <t>A red light isn't the desired state in testing but it sure helps when riding your bike at night. Water-resistant with 3 lighting modes, 1 AAA battery included.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/bike-light-1200x1500.37c843b09a7d77409d63.jpg</t>
+    <t>https://www.saucedemo.com/assets/bike-light-1200x1500-DxcZRFOA.jpg</t>
   </si>
   <si>
     <t>Sauce Labs Bolt T-Shirt</t>
@@ -1091,7 +1179,7 @@
     <t>Get your testing superhero on with the Sauce Labs bolt T-shirt. From American Apparel, 100% ringspun combed cotton, heather gray with red bolt.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/bolt-shirt-1200x1500.c2599ac5f0a35ed5931e.jpg</t>
+    <t>https://www.saucedemo.com/assets/bolt-shirt-1200x1500-mR0ldpVS.jpg</t>
   </si>
   <si>
     <t>Sauce Labs Fleece Jacket</t>
@@ -1103,7 +1191,7 @@
     <t>It's not every day that you come across a midweight quarter-zip fleece jacket capable of handling everything from a relaxing day outdoors to a busy day at the office.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/sauce-pullover-1200x1500.51d7ffaf301e698772c8.jpg</t>
+    <t>https://www.saucedemo.com/assets/sauce-pullover-1200x1500-BfbI-PSd.jpg</t>
   </si>
   <si>
     <t>Sauce Labs Onesie</t>
@@ -1115,7 +1203,7 @@
     <t>Rib snap infant onesie for the junior automation engineer in development. Reinforced 3-snap bottom closure, two-needle hemmed sleeved and bottom won't unravel.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/red-onesie-1200x1500.2ec615b271ef4c3bc430.jpg</t>
+    <t>https://www.saucedemo.com/assets/red-onesie-1200x1500-BrSuq0ic.jpg</t>
   </si>
   <si>
     <t>Test.allTheThings() T-Shirt (Red)</t>
@@ -1124,7 +1212,7 @@
     <t>This classic Sauce Labs t-shirt is perfect to wear when cozying up to your keyboard to automate a few tests. Super-soft and comfy ringspun combed cotton.</t>
   </si>
   <si>
-    <t>https://www.saucedemo.com/static/media/red-tatt-1200x1500.30dadef477804e54fc7b.jpg</t>
+    <t>https://www.saucedemo.com/assets/red-tatt-1200x1500-E-qp6aYf.jpg</t>
   </si>
   <si>
     <t>Sauce Labs Backpack - $29.99</t>
@@ -1145,925 +1233,763 @@
     <t>Test.allTheThings() T-Shirt (Red) - $15.99</t>
   </si>
   <si>
-    <t>02-07-2026 11:48:18</t>
-  </si>
-  <si>
-    <t>02-07-2026 11:50:56</t>
-  </si>
-  <si>
-    <t>02-07-2026 13:37:54</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>05-07-2026 13:13:57</t>
+    <t>11-07-2026 21:43:24</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>2.68%</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>1.75%</t>
+  </si>
+  <si>
+    <t>Added</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:45</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:46</t>
+  </si>
+  <si>
+    <t>Removed</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:47</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Error Message</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:43:56</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:01</t>
+  </si>
+  <si>
+    <t>41.49%</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>560001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:05</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Error: First Name is required</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:18</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:20</t>
+  </si>
+  <si>
+    <t>20.84%</t>
+  </si>
+  <si>
+    <t>Error: Last Name is required</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:32</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:35</t>
+  </si>
+  <si>
+    <t>17.36%</t>
+  </si>
+  <si>
+    <t>Error: Postal Code is required</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:43</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:45</t>
+  </si>
+  <si>
+    <t>36.27%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:50</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:44:57</t>
+  </si>
+  <si>
+    <t>5.44%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:45:07</t>
+  </si>
+  <si>
+    <t>24.63%</t>
+  </si>
+  <si>
+    <t>22.94%</t>
+  </si>
+  <si>
+    <t>13.58%</t>
+  </si>
+  <si>
+    <t>14.25%</t>
+  </si>
+  <si>
+    <t>13.29%</t>
+  </si>
+  <si>
+    <t>19.56%</t>
+  </si>
+  <si>
+    <t>8.75%</t>
+  </si>
+  <si>
+    <t>SauceDemo Logo</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:46:06</t>
   </si>
   <si>
     <t>Login Button Alignment</t>
   </si>
   <si>
-    <t>09-07-2026 06:42:44</t>
+    <t>11-07-2026 21:46:14</t>
+  </si>
+  <si>
+    <t>4.17%</t>
   </si>
   <si>
     <t>Inventory Layout</t>
   </si>
   <si>
-    <t>09-07-2026 06:42:49</t>
+    <t>11-07-2026 21:46:23</t>
+  </si>
+  <si>
+    <t>3.33%</t>
   </si>
   <si>
     <t>Cart Icon</t>
   </si>
   <si>
-    <t>09-07-2026 06:42:53</t>
+    <t>11-07-2026 21:46:30</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:46:34</t>
+  </si>
+  <si>
+    <t>29.23%</t>
   </si>
   <si>
     <t>Footer Links</t>
   </si>
   <si>
-    <t>09-07-2026 06:42:58</t>
-  </si>
-  <si>
-    <t>09-07-2026 06:52:49</t>
-  </si>
-  <si>
-    <t>09-07-2026 06:52:53</t>
-  </si>
-  <si>
-    <t>09-07-2026 06:52:57</t>
-  </si>
-  <si>
-    <t>09-07-2026 06:53:02</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:12:37</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:12:45</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:12:49</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:16:43</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:16:47</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:16:51</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:16:55</t>
-  </si>
-  <si>
-    <t>SauceDemo Logo</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:23:56</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:23:58</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:24:01</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:24:04</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:24:07</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:32:31</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:32:36</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:32:38</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:32:41</t>
-  </si>
-  <si>
-    <t>09-07-2026 07:32:43</t>
-  </si>
-  <si>
-    <t>09-07-2026 10:52:12</t>
-  </si>
-  <si>
-    <t>09-07-2026 10:52:20</t>
-  </si>
-  <si>
-    <t>09-07-2026 10:52:26</t>
-  </si>
-  <si>
-    <t>09-07-2026 10:52:34</t>
-  </si>
-  <si>
-    <t>09-07-2026 10:52:39</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Expected Error</t>
-  </si>
-  <si>
-    <t>Actual Error</t>
-  </si>
-  <si>
-    <t>Username and password do not match any user in this service</t>
-  </si>
-  <si>
-    <t>Epic sadface: Username and password do not match any user in this service</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:00:33</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:00:39</t>
-  </si>
-  <si>
-    <t>Username is required</t>
-  </si>
-  <si>
-    <t>Epic sadface: Username is required</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:00:44</t>
-  </si>
-  <si>
-    <t>Sorry, this user has been locked out.</t>
-  </si>
-  <si>
-    <t>Epic sadface: Sorry, this user has been locked out.</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:00:50</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/sauce-backpack-1200x1500-CjRW-Djj.jpg</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:01:30</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/bike-light-1200x1500-DxcZRFOA.jpg</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/bolt-shirt-1200x1500-mR0ldpVS.jpg</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/sauce-pullover-1200x1500-BfbI-PSd.jpg</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/red-onesie-1200x1500-BrSuq0ic.jpg</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/assets/red-tatt-1200x1500-E-qp6aYf.jpg</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Added</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:02:30</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:02:31</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:02:55</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:02:56</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:03:25</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:03:26</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>Error Message</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>560001</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Error: First Name is required</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:04:24</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Error: Last Name is required</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:04:30</t>
-  </si>
-  <si>
-    <t>Error: Postal Code is required</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:04:37</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:05:16</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:07:16</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:07:24</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:07:29</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:07:35</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:07:40</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:28</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:29</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:37</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:44</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:52</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:10:59</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:06</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:32</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:37</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:42</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:47</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:11:53</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:12:44</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:12:49</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:12:53</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:12:59</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:13:04</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:17:26</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:17:32</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:17:37</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:17:42</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:19:57</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:21:15</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:22:14</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:24:21</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:24:27</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:24:34</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:25:33</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:26:41</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:26:49</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:26:55</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:27:00</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:27:06</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:50:39</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:50:47</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:50:54</t>
-  </si>
-  <si>
-    <t>09-07-2026 14:51:05</t>
-  </si>
-  <si>
-    <t>09-07-2026 15:13:47</t>
-  </si>
-  <si>
-    <t>09-07-2026 15:13:56</t>
-  </si>
-  <si>
-    <t>09-07-2026 15:14:07</t>
-  </si>
-  <si>
-    <t>09-07-2026 16:41:41</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:36:58</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:37:04</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:37:09</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:37:14</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:37:19</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:40:44</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:40:51</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:40:57</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:41:03</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:41:09</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:47:20</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:47:21</t>
-  </si>
-  <si>
-    <t>Removed</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:03</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:10</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:37</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:43</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:49</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:48:56</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:49:02</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:24</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:30</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:36</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:41</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:46</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:51</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:50:56</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:51:02</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:05</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:11</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:19</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:26</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:33</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:50</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:15:51</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:16:15</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:16:20</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:16:26</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:16:32</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:21</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:26</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:31</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:36</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:41</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:17:55</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:18:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:18:07</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:25:17</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:25:23</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:25:31</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:25:38</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:25:48</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:06</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:07</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:14</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:20</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:25</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:31</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:26:38</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:27:26</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:27:32</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:27:37</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:27:42</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:27:47</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:28:01</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:28:06</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:28:11</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:32:05</t>
-  </si>
-  <si>
-    <t>edge</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:32:12</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:32:18</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:32:27</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:12</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:18</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:23</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:30</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:37</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:57</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:46:58</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:47:06</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:47:13</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:47:20</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:47:27</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:47:33</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:48:26</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:48:31</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:48:36</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:48:41</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:48:47</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:49:03</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:49:09</t>
-  </si>
-  <si>
-    <t>11-07-2026 12:49:15</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:05:43</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:06:54</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:06:55</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:08:13</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:08:14</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:12:56</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:13:03</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:13:10</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:13:17</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:14:02</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:14:09</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:14:15</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:14:21</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:20:07</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:20:14</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:20:15</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:20:24</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:20:34</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:33:47</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:33:48</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:33:57</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:34:06</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:34:15</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:45:58</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:05</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:09</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:11</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:17</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:18</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:46:24</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:57:33</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:57:42</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:57:49</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:57:52</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:57:56</t>
-  </si>
-  <si>
-    <t>11-07-2026 13:58:10</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:06</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:11</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:14</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:21</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:24</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:30</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:34</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:37</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:46</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:54:51</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:14</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:15</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:16</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:24</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:25</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:27</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:38</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:55:50</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:56:01</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:56:02</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:56:13</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:56:27</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:57:38</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:57:46</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:57:54</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:00</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:03</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:10</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:12</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:19</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:29</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:33</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:39</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:58:44</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:59:00</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:59:07</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:59:13</t>
-  </si>
-  <si>
-    <t>11-07-2026 14:59:20</t>
-  </si>
-  <si>
-    <t>11-07-2026 15:36:45</t>
-  </si>
-  <si>
-    <t>11-07-2026 15:36:46</t>
-  </si>
-  <si>
-    <t>11-07-2026 15:47:56</t>
-  </si>
-  <si>
-    <t>11-07-2026 15:47:57</t>
-  </si>
-  <si>
-    <t>11-07-2026 15:54:11</t>
-  </si>
-  <si>
-    <t>11-07-2026 16:00:37</t>
-  </si>
-  <si>
-    <t>11-07-2026 16:00:38</t>
-  </si>
-  <si>
-    <t>11-07-2026 17:08:28</t>
+    <t>11-07-2026 21:46:41</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:46:49</t>
+  </si>
+  <si>
+    <t>37.44%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:01</t>
+  </si>
+  <si>
+    <t>25.05%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:04</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:10</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:12</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:17</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:20</t>
+  </si>
+  <si>
+    <t>31.61%</t>
+  </si>
+  <si>
+    <t>22.49%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:34</t>
+  </si>
+  <si>
+    <t>16.88%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:39</t>
+  </si>
+  <si>
+    <t>29.64%</t>
+  </si>
+  <si>
+    <t>11-07-2026 21:47:45</t>
+  </si>
+  <si>
+    <t>22.23%</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:49:48</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:52:04</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:52:06</t>
+  </si>
+  <si>
+    <t>6.77%</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:53:19</t>
+  </si>
+  <si>
+    <t>4.32%</t>
+  </si>
+  <si>
+    <t>5.48%</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:05</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:06</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:07</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:08</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:10</t>
+  </si>
+  <si>
+    <t>11-07-2026 22:57:11</t>
+  </si>
+  <si>
+    <t>14.37%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:41:38</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:41:43</t>
+  </si>
+  <si>
+    <t>21.59%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:41:53</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:41:56</t>
+  </si>
+  <si>
+    <t>8.42%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:42:05</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:42:12</t>
+  </si>
+  <si>
+    <t>18.55%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:44:45</t>
+  </si>
+  <si>
+    <t>0.81%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:45:00</t>
+  </si>
+  <si>
+    <t>0.39%</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:45:18</t>
+  </si>
+  <si>
+    <t>12-07-2026 00:45:19</t>
+  </si>
+  <si>
+    <t>0.75%</t>
+  </si>
+  <si>
+    <t>31.93%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:38:36</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:38:40</t>
+  </si>
+  <si>
+    <t>11.53%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:38:59</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:39:07</t>
+  </si>
+  <si>
+    <t>18.53%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:39:21</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:39:30</t>
+  </si>
+  <si>
+    <t>12.88%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:39:42</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:39:56</t>
+  </si>
+  <si>
+    <t>22.43%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:40:11</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:40:38</t>
+  </si>
+  <si>
+    <t>14.12%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:03</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:05</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:06</t>
+  </si>
+  <si>
+    <t>3.39%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:23</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:25</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:27</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:28</t>
+  </si>
+  <si>
+    <t>2.34%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:38</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:47</t>
+  </si>
+  <si>
+    <t>13.24%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:41:51</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:42:08</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:42:09</t>
+  </si>
+  <si>
+    <t>34.79%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:42:28</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:42:37</t>
+  </si>
+  <si>
+    <t>50.21%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:42:58</t>
+  </si>
+  <si>
+    <t>11.14%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:43:25</t>
+  </si>
+  <si>
+    <t>30.98%</t>
+  </si>
+  <si>
+    <t>35.51%</t>
+  </si>
+  <si>
+    <t>3.34%</t>
+  </si>
+  <si>
+    <t>21.90%</t>
+  </si>
+  <si>
+    <t>0.36%</t>
+  </si>
+  <si>
+    <t>42.97%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:45:23</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:45:34</t>
+  </si>
+  <si>
+    <t>7.05%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:45:45</t>
+  </si>
+  <si>
+    <t>21.86%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:45:54</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:03</t>
+  </si>
+  <si>
+    <t>8.66%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:18</t>
+  </si>
+  <si>
+    <t>8.14%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:28</t>
+  </si>
+  <si>
+    <t>12.97%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:33</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:40</t>
+  </si>
+  <si>
+    <t>14.31%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:53</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:46:54</t>
+  </si>
+  <si>
+    <t>41.58%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:47:08</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:47:09</t>
+  </si>
+  <si>
+    <t>39.17%</t>
+  </si>
+  <si>
+    <t>4.69%</t>
+  </si>
+  <si>
+    <t>14.38%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:47:42</t>
+  </si>
+  <si>
+    <t>3.75%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:47:54</t>
+  </si>
+  <si>
+    <t>40.52%</t>
+  </si>
+  <si>
+    <t>12-07-2026 16:48:07</t>
+  </si>
+  <si>
+    <t>12.63%</t>
+  </si>
+  <si>
+    <t>3.36%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:02</t>
+  </si>
+  <si>
+    <t>12.52%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:14</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:16</t>
+  </si>
+  <si>
+    <t>11.08%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:27</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:33</t>
+  </si>
+  <si>
+    <t>24.59%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:38</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:03:44</t>
+  </si>
+  <si>
+    <t>0.40%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:04:00</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:04:07</t>
+  </si>
+  <si>
+    <t>12.41%</t>
+  </si>
+  <si>
+    <t>9.49%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:04:56</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:04:59</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:00</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:02</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:04</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:05</t>
+  </si>
+  <si>
+    <t>13.13%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:26</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:30</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:48</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:05:51</t>
+  </si>
+  <si>
+    <t>3.77%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:06</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:09</t>
+  </si>
+  <si>
+    <t>12.76%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:23</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:26</t>
+  </si>
+  <si>
+    <t>1.44%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:38</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:06:43</t>
+  </si>
+  <si>
+    <t>22.91%</t>
+  </si>
+  <si>
+    <t>33.24%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>1.68%</t>
+  </si>
+  <si>
+    <t>1.37%</t>
+  </si>
+  <si>
+    <t>1.33%</t>
+  </si>
+  <si>
+    <t>15.21%</t>
+  </si>
+  <si>
+    <t>13.84%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:03</t>
+  </si>
+  <si>
+    <t>21.51%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:20</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:37</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:38</t>
+  </si>
+  <si>
+    <t>24.93%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:53</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:09:56</t>
+  </si>
+  <si>
+    <t>12.75%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:10:07</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:10:15</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:10:30</t>
+  </si>
+  <si>
+    <t>6.81%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:10:44</t>
+  </si>
+  <si>
+    <t>3.86%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:10:50</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:11:02</t>
+  </si>
+  <si>
+    <t>5.20%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:11:16</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:11:20</t>
+  </si>
+  <si>
+    <t>23.06%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:11:28</t>
+  </si>
+  <si>
+    <t>35.67%</t>
+  </si>
+  <si>
+    <t>12-07-2026 17:11:39</t>
+  </si>
+  <si>
+    <t>22.74%</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +1997,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2124,6 +2050,36 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -2394,7 +2350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="330">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2523,6 +2479,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2532,69 +2512,129 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment wrapText="true" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment wrapText="true" vertical="center"/>
+      <alignment wrapText="false" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment wrapText="true" vertical="center" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment wrapText="true" vertical="center" horizontal="left"/>
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
@@ -2604,11 +2644,692 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment wrapText="false" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment wrapText="false" vertical="center"/>
@@ -3619,187 +4340,201 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="20.0"/>
+    <col min="2" max="2" customWidth="true" width="40.0"/>
+    <col min="3" max="3" customWidth="true" width="15.0"/>
+    <col min="4" max="4" customWidth="true" width="25.0"/>
+    <col min="5" max="5" customWidth="true" width="12.0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>422</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B2" t="s" s="0">
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="109">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="109">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s" s="109">
         <v>330</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>631</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>632</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D4" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>632</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>505</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>633</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>634</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>635</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>635</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>505</v>
-      </c>
-      <c r="D9" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>635</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>334</v>
+      <c r="D1" t="s" s="109">
+        <v>331</v>
+      </c>
+      <c r="E1" t="s" s="109">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="303">
+        <v>245</v>
+      </c>
+      <c r="B2" t="s" s="303">
+        <v>438</v>
+      </c>
+      <c r="C2" t="s" s="303">
+        <v>337</v>
+      </c>
+      <c r="D2" t="s" s="303">
+        <v>617</v>
+      </c>
+      <c r="E2" t="s" s="303">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="305">
+        <v>248</v>
+      </c>
+      <c r="B3" t="s" s="305">
+        <v>440</v>
+      </c>
+      <c r="C3" t="s" s="305">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s" s="305">
+        <v>619</v>
+      </c>
+      <c r="E3" t="s" s="305">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" ht="25.0" customHeight="true">
+      <c r="A4" t="s" s="306">
+        <v>251</v>
+      </c>
+      <c r="B4" t="s" s="306">
+        <v>443</v>
+      </c>
+      <c r="C4" t="s" s="306">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s" s="306">
+        <v>620</v>
+      </c>
+      <c r="E4" t="s" s="306">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="25.0" customHeight="true">
+      <c r="A5" t="s" s="307">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s" s="307">
+        <v>438</v>
+      </c>
+      <c r="C5" t="s" s="307">
+        <v>337</v>
+      </c>
+      <c r="D5" t="s" s="307">
+        <v>621</v>
+      </c>
+      <c r="E5" t="s" s="307">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="25.0" customHeight="true">
+      <c r="A6" t="s" s="309">
+        <v>255</v>
+      </c>
+      <c r="B6" t="s" s="309">
+        <v>446</v>
+      </c>
+      <c r="C6" t="s" s="309">
+        <v>337</v>
+      </c>
+      <c r="D6" t="s" s="309">
+        <v>623</v>
+      </c>
+      <c r="E6" t="s" s="309">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" ht="25.0" customHeight="true">
+      <c r="A7" t="s" s="310">
+        <v>248</v>
+      </c>
+      <c r="B7" t="s" s="310">
+        <v>440</v>
+      </c>
+      <c r="C7" t="s" s="310">
+        <v>337</v>
+      </c>
+      <c r="D7" t="s" s="310">
+        <v>624</v>
+      </c>
+      <c r="E7" t="s" s="310">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" ht="25.0" customHeight="true">
+      <c r="A8" t="s" s="312">
+        <v>257</v>
+      </c>
+      <c r="B8" t="s" s="312">
+        <v>450</v>
+      </c>
+      <c r="C8" t="s" s="312">
+        <v>337</v>
+      </c>
+      <c r="D8" t="s" s="312">
+        <v>626</v>
+      </c>
+      <c r="E8" t="s" s="312">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" ht="25.0" customHeight="true">
+      <c r="A9" t="s" s="313">
+        <v>251</v>
+      </c>
+      <c r="B9" t="s" s="313">
+        <v>443</v>
+      </c>
+      <c r="C9" t="s" s="313">
+        <v>337</v>
+      </c>
+      <c r="D9" t="s" s="313">
+        <v>627</v>
+      </c>
+      <c r="E9" t="s" s="313">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" ht="25.0" customHeight="true">
+      <c r="A10" t="s" s="315">
+        <v>255</v>
+      </c>
+      <c r="B10" t="s" s="315">
+        <v>446</v>
+      </c>
+      <c r="C10" t="s" s="315">
+        <v>337</v>
+      </c>
+      <c r="D10" t="s" s="315">
+        <v>628</v>
+      </c>
+      <c r="E10" t="s" s="315">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" ht="25.0" customHeight="true">
+      <c r="A11" t="s" s="317">
+        <v>257</v>
+      </c>
+      <c r="B11" t="s" s="317">
+        <v>450</v>
+      </c>
+      <c r="C11" t="s" s="317">
+        <v>337</v>
+      </c>
+      <c r="D11" t="s" s="317">
+        <v>630</v>
+      </c>
+      <c r="E11" t="s" s="317">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -3809,229 +4544,126 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>431</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>432</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>433</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>434</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>453</v>
-      </c>
-      <c r="G2" t="s" s="0">
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="124">
+        <v>261</v>
+      </c>
+      <c r="B1" t="s" s="124">
+        <v>262</v>
+      </c>
+      <c r="C1" t="s" s="124">
+        <v>337</v>
+      </c>
+      <c r="D1" t="s" s="124">
+        <v>456</v>
+      </c>
+      <c r="E1" t="s" s="124">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="319">
+        <v>261</v>
+      </c>
+      <c r="B2" t="s" s="319">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s" s="319">
+        <v>337</v>
+      </c>
+      <c r="D2" t="s" s="319">
+        <v>632</v>
+      </c>
+      <c r="E2" t="s" s="319">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="321">
+        <v>264</v>
+      </c>
+      <c r="B3" t="s" s="321">
+        <v>265</v>
+      </c>
+      <c r="C3" t="s" s="321">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s" s="321">
+        <v>633</v>
+      </c>
+      <c r="E3" t="s" s="321">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" ht="25.0" customHeight="true">
+      <c r="A4" t="s" s="323">
+        <v>267</v>
+      </c>
+      <c r="B4" t="s" s="323">
+        <v>268</v>
+      </c>
+      <c r="C4" t="s" s="323">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s" s="323">
+        <v>635</v>
+      </c>
+      <c r="E4" t="s" s="323">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="25.0" customHeight="true">
+      <c r="A5" t="s" s="324">
+        <v>261</v>
+      </c>
+      <c r="B5" t="s" s="324">
+        <v>262</v>
+      </c>
+      <c r="C5" t="s" s="324">
+        <v>337</v>
+      </c>
+      <c r="D5" t="s" s="324">
         <v>636</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>453</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>637</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="B4" s="0"/>
-      <c r="C4" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>438</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>637</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C5" s="0"/>
-      <c r="D5" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="G5" t="s" s="0">
+      <c r="E5" t="s" s="324">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="25.0" customHeight="true">
+      <c r="A6" t="s" s="326">
+        <v>264</v>
+      </c>
+      <c r="B6" t="s" s="326">
+        <v>265</v>
+      </c>
+      <c r="C6" t="s" s="326">
+        <v>337</v>
+      </c>
+      <c r="D6" t="s" s="326">
         <v>638</v>
       </c>
-      <c r="H5" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="B6" s="0"/>
-      <c r="C6" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>438</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>638</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C7" s="0"/>
-      <c r="D7" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>639</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>169</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D8" s="0"/>
-      <c r="E8" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>443</v>
-      </c>
-      <c r="G8" t="s" s="0">
+      <c r="E6" t="s" s="326">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" ht="25.0" customHeight="true">
+      <c r="A7" t="s" s="328">
+        <v>267</v>
+      </c>
+      <c r="B7" t="s" s="328">
+        <v>268</v>
+      </c>
+      <c r="C7" t="s" s="328">
+        <v>337</v>
+      </c>
+      <c r="D7" t="s" s="328">
         <v>640</v>
       </c>
-      <c r="H8" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>169</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="D9" s="0"/>
-      <c r="E9" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>443</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>641</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>334</v>
+      <c r="E7" t="s" s="328">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -4039,376 +4671,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>489</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>490</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>491</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>513</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>514</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>515</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>537</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>538</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>539</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>557</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>558</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>559</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>582</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>583</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>584</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>652</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>654</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>655</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>261</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>656</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>657</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>658</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.0"/>
@@ -4424,227 +4689,347 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.0" customHeight="true">
-      <c r="A1" t="s" s="72">
-        <v>309</v>
-      </c>
-      <c r="B1" t="s" s="72">
-        <v>310</v>
-      </c>
-      <c r="C1" t="s" s="72">
+      <c r="A1" t="s" s="253">
+        <v>355</v>
+      </c>
+      <c r="B1" t="s" s="253">
+        <v>356</v>
+      </c>
+      <c r="C1" t="s" s="253">
         <v>3</v>
       </c>
-      <c r="D1" t="s" s="72">
-        <v>311</v>
-      </c>
-      <c r="E1" t="s" s="72">
-        <v>312</v>
-      </c>
-      <c r="F1" t="s" s="72">
-        <v>313</v>
-      </c>
-      <c r="G1" t="s" s="72">
+      <c r="D1" t="s" s="253">
+        <v>357</v>
+      </c>
+      <c r="E1" t="s" s="253">
+        <v>358</v>
+      </c>
+      <c r="F1" t="s" s="253">
+        <v>359</v>
+      </c>
+      <c r="G1" t="s" s="253">
         <v>131</v>
       </c>
-      <c r="H1" t="s" s="72">
+      <c r="H1" t="s" s="253">
         <v>135</v>
       </c>
-      <c r="I1" t="s" s="72">
-        <v>316</v>
-      </c>
-      <c r="J1" t="s" s="72">
-        <v>317</v>
+      <c r="I1" t="s" s="253">
+        <v>331</v>
+      </c>
+      <c r="J1" t="s" s="253">
+        <v>332</v>
       </c>
     </row>
     <row r="2" ht="30.0" customHeight="true">
-      <c r="A2" t="s" s="74">
-        <v>191</v>
-      </c>
-      <c r="B2" t="s" s="74">
-        <v>330</v>
-      </c>
-      <c r="C2" t="s" s="74">
-        <v>331</v>
-      </c>
-      <c r="D2" t="s" s="74">
-        <v>414</v>
+      <c r="A2" t="s" s="268">
+        <v>192</v>
+      </c>
+      <c r="B2" t="s" s="268">
+        <v>360</v>
+      </c>
+      <c r="C2" t="s" s="268">
+        <v>361</v>
+      </c>
+      <c r="D2" t="s" s="268">
+        <v>362</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="I2" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J2" t="s" s="74">
-        <v>334</v>
+        <v>386</v>
+      </c>
+      <c r="I2" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J2" t="s" s="268">
+        <v>339</v>
       </c>
     </row>
     <row r="3" ht="30.0" customHeight="true">
-      <c r="A3" t="s" s="74">
-        <v>335</v>
-      </c>
-      <c r="B3" t="s" s="74">
-        <v>336</v>
-      </c>
-      <c r="C3" t="s" s="74">
-        <v>337</v>
-      </c>
-      <c r="D3" t="s" s="74">
-        <v>416</v>
+      <c r="A3" t="s" s="268">
+        <v>364</v>
+      </c>
+      <c r="B3" t="s" s="268">
+        <v>365</v>
+      </c>
+      <c r="C3" t="s" s="268">
+        <v>366</v>
+      </c>
+      <c r="D3" t="s" s="268">
+        <v>367</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="I3" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J3" t="s" s="74">
-        <v>334</v>
+        <v>383</v>
+      </c>
+      <c r="I3" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J3" t="s" s="268">
+        <v>339</v>
       </c>
     </row>
     <row r="4" ht="30.0" customHeight="true">
-      <c r="A4" t="s" s="74">
+      <c r="A4" t="s" s="268">
+        <v>368</v>
+      </c>
+      <c r="B4" t="s" s="268">
+        <v>369</v>
+      </c>
+      <c r="C4" t="s" s="268">
+        <v>370</v>
+      </c>
+      <c r="D4" t="s" s="268">
+        <v>371</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="I4" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J4" t="s" s="268">
         <v>339</v>
       </c>
-      <c r="B4" t="s" s="74">
-        <v>340</v>
-      </c>
-      <c r="C4" t="s" s="74">
+    </row>
+    <row r="5" ht="30.0" customHeight="true">
+      <c r="A5" t="s" s="268">
+        <v>372</v>
+      </c>
+      <c r="B5" t="s" s="268">
+        <v>373</v>
+      </c>
+      <c r="C5" t="s" s="268">
+        <v>374</v>
+      </c>
+      <c r="D5" t="s" s="268">
+        <v>375</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="I5" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J5" t="s" s="268">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" ht="30.0" customHeight="true">
+      <c r="A6" t="s" s="268">
+        <v>376</v>
+      </c>
+      <c r="B6" t="s" s="268">
+        <v>377</v>
+      </c>
+      <c r="C6" t="s" s="268">
+        <v>378</v>
+      </c>
+      <c r="D6" t="s" s="268">
+        <v>379</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="I6" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J6" t="s" s="268">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" ht="30.0" customHeight="true">
+      <c r="A7" t="s" s="268">
+        <v>380</v>
+      </c>
+      <c r="B7" t="s" s="268">
+        <v>369</v>
+      </c>
+      <c r="C7" t="s" s="268">
+        <v>381</v>
+      </c>
+      <c r="D7" t="s" s="268">
+        <v>382</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="I7" t="s" s="268">
+        <v>584</v>
+      </c>
+      <c r="J7" t="s" s="268">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" ht="30.0" customHeight="true">
+      <c r="A8" t="s" s="269">
+        <v>192</v>
+      </c>
+      <c r="B8" t="s" s="269">
+        <v>360</v>
+      </c>
+      <c r="C8" t="s" s="269">
+        <v>361</v>
+      </c>
+      <c r="D8" t="s" s="269">
+        <v>362</v>
+      </c>
+      <c r="I8" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J8" t="s" s="269">
         <v>341</v>
       </c>
-      <c r="D4" t="s" s="74">
-        <v>417</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="I4" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J4" t="s" s="74">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" ht="30.0" customHeight="true">
-      <c r="A5" t="s" s="74">
-        <v>343</v>
-      </c>
-      <c r="B5" t="s" s="74">
-        <v>344</v>
-      </c>
-      <c r="C5" t="s" s="74">
-        <v>345</v>
-      </c>
-      <c r="D5" t="s" s="74">
-        <v>418</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="I5" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J5" t="s" s="74">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6" ht="30.0" customHeight="true">
-      <c r="A6" t="s" s="74">
-        <v>347</v>
-      </c>
-      <c r="B6" t="s" s="74">
-        <v>348</v>
-      </c>
-      <c r="C6" t="s" s="74">
-        <v>349</v>
-      </c>
-      <c r="D6" t="s" s="74">
-        <v>419</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="I6" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J6" t="s" s="74">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7" ht="30.0" customHeight="true">
-      <c r="A7" t="s" s="74">
-        <v>351</v>
-      </c>
-      <c r="B7" t="s" s="74">
-        <v>340</v>
-      </c>
-      <c r="C7" t="s" s="74">
-        <v>352</v>
-      </c>
-      <c r="D7" t="s" s="74">
-        <v>420</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="I7" t="s" s="74">
-        <v>666</v>
-      </c>
-      <c r="J7" t="s" s="74">
-        <v>334</v>
+    </row>
+    <row r="9" ht="30.0" customHeight="true">
+      <c r="A9" t="s" s="269">
+        <v>364</v>
+      </c>
+      <c r="B9" t="s" s="269">
+        <v>365</v>
+      </c>
+      <c r="C9" t="s" s="269">
+        <v>366</v>
+      </c>
+      <c r="D9" t="s" s="269">
+        <v>367</v>
+      </c>
+      <c r="I9" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J9" t="s" s="269">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" ht="30.0" customHeight="true">
+      <c r="A10" t="s" s="269">
+        <v>368</v>
+      </c>
+      <c r="B10" t="s" s="269">
+        <v>369</v>
+      </c>
+      <c r="C10" t="s" s="269">
+        <v>370</v>
+      </c>
+      <c r="D10" t="s" s="269">
+        <v>371</v>
+      </c>
+      <c r="I10" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J10" t="s" s="269">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" ht="30.0" customHeight="true">
+      <c r="A11" t="s" s="269">
+        <v>372</v>
+      </c>
+      <c r="B11" t="s" s="269">
+        <v>373</v>
+      </c>
+      <c r="C11" t="s" s="269">
+        <v>374</v>
+      </c>
+      <c r="D11" t="s" s="269">
+        <v>375</v>
+      </c>
+      <c r="I11" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J11" t="s" s="269">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" ht="30.0" customHeight="true">
+      <c r="A12" t="s" s="269">
+        <v>376</v>
+      </c>
+      <c r="B12" t="s" s="269">
+        <v>377</v>
+      </c>
+      <c r="C12" t="s" s="269">
+        <v>378</v>
+      </c>
+      <c r="D12" t="s" s="269">
+        <v>379</v>
+      </c>
+      <c r="I12" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J12" t="s" s="269">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" ht="30.0" customHeight="true">
+      <c r="A13" t="s" s="269">
+        <v>380</v>
+      </c>
+      <c r="B13" t="s" s="269">
+        <v>369</v>
+      </c>
+      <c r="C13" t="s" s="269">
+        <v>381</v>
+      </c>
+      <c r="D13" t="s" s="269">
+        <v>382</v>
+      </c>
+      <c r="I13" t="s" s="269">
+        <v>585</v>
+      </c>
+      <c r="J13" t="s" s="269">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -4670,15 +5055,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="35.25" customHeight="1">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" s="14" customFormat="1" ht="35.25" customHeight="1">
@@ -4711,7 +5096,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="46" t="s">
         <v>77</v>
       </c>
       <c r="B3" s="22" t="s">
@@ -4736,7 +5121,7 @@
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A4" s="48"/>
+      <c r="A4" s="47"/>
       <c r="B4" s="22" t="s">
         <v>84</v>
       </c>
@@ -4759,7 +5144,7 @@
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A5" s="48"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="22" t="s">
         <v>90</v>
       </c>
@@ -4782,7 +5167,7 @@
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A6" s="48"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="23" t="s">
         <v>94</v>
       </c>
@@ -4805,7 +5190,7 @@
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1">
-      <c r="A7" s="49"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="22" t="s">
         <v>99</v>
       </c>
@@ -4828,7 +5213,7 @@
       <c r="I7" s="28"/>
     </row>
     <row r="8" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="46" t="s">
         <v>103</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -4853,7 +5238,7 @@
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A9" s="53"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="25" t="s">
         <v>110</v>
       </c>
@@ -4876,7 +5261,7 @@
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="24" t="s">
         <v>113</v>
       </c>
@@ -4899,7 +5284,7 @@
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A11" s="54"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="24" t="s">
         <v>116</v>
       </c>
@@ -4922,7 +5307,7 @@
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="47" t="s">
         <v>119</v>
       </c>
       <c r="B12" s="24" t="s">
@@ -4947,7 +5332,7 @@
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A13" s="48"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="24" t="s">
         <v>125</v>
       </c>
@@ -4970,7 +5355,7 @@
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A14" s="48"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="24" t="s">
         <v>129</v>
       </c>
@@ -4993,7 +5378,7 @@
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A15" s="49"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="24" t="s">
         <v>133</v>
       </c>
@@ -5016,7 +5401,7 @@
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="49" t="s">
         <v>136</v>
       </c>
       <c r="B16" s="24" t="s">
@@ -5039,7 +5424,7 @@
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A17" s="49"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="24" t="s">
         <v>141</v>
       </c>
@@ -5083,7 +5468,7 @@
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="49" t="s">
         <v>150</v>
       </c>
       <c r="B19" s="24" t="s">
@@ -5106,7 +5491,7 @@
       <c r="I19" s="27"/>
     </row>
     <row r="20" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A20" s="49"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="24" t="s">
         <v>155</v>
       </c>
@@ -5127,7 +5512,7 @@
       <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="49" t="s">
         <v>158</v>
       </c>
       <c r="B21" s="24" t="s">
@@ -5150,7 +5535,7 @@
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A22" s="48"/>
+      <c r="A22" s="47"/>
       <c r="B22" s="24" t="s">
         <v>164</v>
       </c>
@@ -5171,7 +5556,7 @@
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A23" s="48"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="24" t="s">
         <v>167</v>
       </c>
@@ -5192,7 +5577,7 @@
       <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A24" s="49"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="24" t="s">
         <v>169</v>
       </c>
@@ -5264,33 +5649,33 @@
         <v>180</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A28" s="47" t="s">
-        <v>183</v>
+      <c r="A28" s="49" t="s">
+        <v>184</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>107</v>
@@ -5303,163 +5688,163 @@
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A29" s="49"/>
+      <c r="A29" s="48"/>
       <c r="B29" s="23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="28"/>
     </row>
     <row r="30" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A30" s="44" t="s">
-        <v>188</v>
+      <c r="A30" s="52" t="s">
+        <v>189</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A31" s="46"/>
+      <c r="A31" s="54"/>
       <c r="B31" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A32" s="44" t="s">
-        <v>197</v>
+      <c r="A32" s="52" t="s">
+        <v>198</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A33" s="45"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>148</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A34" s="45"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A35" s="45"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A36" s="45"/>
+      <c r="A36" s="53"/>
       <c r="B36" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>153</v>
@@ -5475,57 +5860,57 @@
       <c r="I36" s="27"/>
     </row>
     <row r="37" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A37" s="45"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A38" s="45"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A39" s="46"/>
+      <c r="A39" s="54"/>
       <c r="B39" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>107</v>
@@ -5538,400 +5923,400 @@
       <c r="I39" s="27"/>
     </row>
     <row r="40" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A40" s="44" t="s">
-        <v>223</v>
+      <c r="A40" s="52" t="s">
+        <v>224</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A41" s="45"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="27"/>
     </row>
     <row r="42" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A42" s="45"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="27"/>
     </row>
     <row r="43" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A43" s="46"/>
+      <c r="A43" s="54"/>
       <c r="B43" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="27"/>
     </row>
     <row r="44" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A44" s="44" t="s">
-        <v>239</v>
+      <c r="A44" s="52" t="s">
+        <v>240</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>161</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="27"/>
     </row>
     <row r="45" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A45" s="45"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A46" s="45"/>
+      <c r="A46" s="53"/>
       <c r="B46" s="23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A47" s="45"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="27"/>
     </row>
     <row r="48" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A48" s="45"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="27"/>
     </row>
     <row r="49" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="54"/>
       <c r="B49" s="23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A50" s="44" t="s">
-        <v>259</v>
+      <c r="A50" s="52" t="s">
+        <v>260</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A51" s="45"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="54"/>
       <c r="B52" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="27"/>
     </row>
     <row r="53" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A53" s="44" t="s">
-        <v>271</v>
+      <c r="A53" s="52" t="s">
+        <v>272</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
       <c r="I53" s="27"/>
     </row>
     <row r="54" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A54" s="45"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="27"/>
     </row>
     <row r="55" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A55" s="46"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="27"/>
     </row>
     <row r="56" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A56" s="44" t="s">
-        <v>282</v>
+      <c r="A56" s="52" t="s">
+        <v>283</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A57" s="45"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A58" s="46"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>29</v>
@@ -5947,65 +6332,65 @@
       <c r="I58" s="27"/>
     </row>
     <row r="59" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A59" s="44" t="s">
-        <v>291</v>
+      <c r="A59" s="52" t="s">
+        <v>292</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" s="27"/>
     </row>
     <row r="60" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A60" s="45"/>
+      <c r="A60" s="53"/>
       <c r="B60" s="23" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" s="27"/>
     </row>
     <row r="61" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
@@ -6013,22 +6398,22 @@
     </row>
     <row r="62" spans="1:9" s="2" customFormat="1" ht="35.25" customHeight="1">
       <c r="A62" s="42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
@@ -6037,12 +6422,6 @@
   </sheetData>
   <autoFilter ref="A2:A62" xr:uid="{8187F376-22C9-4E14-9441-9396C4798D74}"/>
   <mergeCells count="16">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A56:A58"/>
@@ -6053,6 +6432,12 @@
     <mergeCell ref="A44:A49"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A32:A39"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6061,7 +6446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE280182-BA0C-4214-9DDE-FF3FDA9A628F}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1"/>
@@ -6074,16 +6459,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" ht="24.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24.75" customHeight="1">
@@ -6091,13 +6476,13 @@
         <v>78</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24.75" customHeight="1">
@@ -6105,13 +6490,13 @@
         <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24.75" customHeight="1">
@@ -6119,13 +6504,13 @@
         <v>90</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.75" customHeight="1">
@@ -6135,7 +6520,7 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24.75" customHeight="1">
@@ -6143,13 +6528,13 @@
         <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -6157,37 +6542,883 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="25.0"/>
+    <col min="2" max="2" customWidth="true" width="18.0"/>
+    <col min="3" max="3" customWidth="true" width="18.0"/>
+    <col min="4" max="4" customWidth="true" width="20.0"/>
+    <col min="5" max="5" customWidth="true" width="18.0"/>
+    <col min="6" max="6" customWidth="true" width="15.0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="56">
         <v>69</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="B1" t="s" s="56">
+        <v>322</v>
+      </c>
+      <c r="C1" t="s" s="56">
+        <v>323</v>
+      </c>
+      <c r="D1" t="s" s="56">
+        <v>324</v>
+      </c>
+      <c r="E1" t="s" s="56">
+        <v>325</v>
+      </c>
+      <c r="F1" t="s" s="56">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="254">
+        <v>78</v>
+      </c>
+      <c r="B2" t="n" s="254">
+        <v>23516.0</v>
+      </c>
+      <c r="C2" t="n" s="254">
+        <v>24333.0</v>
+      </c>
+      <c r="D2" t="s" s="254">
+        <v>390</v>
+      </c>
+      <c r="E2" t="n" s="254">
+        <v>817.0</v>
+      </c>
+      <c r="F2" t="s" s="254">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="258">
+        <v>84</v>
+      </c>
+      <c r="B3" t="n" s="258">
+        <v>13170.0</v>
+      </c>
+      <c r="C3" t="n" s="258">
+        <v>11521.0</v>
+      </c>
+      <c r="D3" t="s" s="258">
+        <v>333</v>
+      </c>
+      <c r="E3" t="n" s="258">
+        <v>1649.0</v>
+      </c>
+      <c r="F3" t="s" s="258">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" ht="25.0" customHeight="true">
+      <c r="A4" t="s" s="261">
+        <v>90</v>
+      </c>
+      <c r="B4" t="n" s="261">
+        <v>12483.0</v>
+      </c>
+      <c r="C4" t="n" s="261">
+        <v>11100.0</v>
+      </c>
+      <c r="D4" t="s" s="261">
+        <v>333</v>
+      </c>
+      <c r="E4" t="n" s="261">
+        <v>1383.0</v>
+      </c>
+      <c r="F4" t="s" s="261">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="5" ht="25.0" customHeight="true">
+      <c r="A5" t="s" s="264">
+        <v>94</v>
+      </c>
+      <c r="B5" t="n" s="264">
+        <v>15632.0</v>
+      </c>
+      <c r="C5" t="n" s="264">
+        <v>11788.0</v>
+      </c>
+      <c r="D5" t="s" s="264">
+        <v>333</v>
+      </c>
+      <c r="E5" t="n" s="264">
+        <v>3844.0</v>
+      </c>
+      <c r="F5" t="s" s="264">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="6" ht="25.0" customHeight="true">
+      <c r="A6" t="s" s="267">
+        <v>99</v>
+      </c>
+      <c r="B6" t="n" s="267">
+        <v>9682.0</v>
+      </c>
+      <c r="C6" t="n" s="267">
+        <v>9721.0</v>
+      </c>
+      <c r="D6" t="s" s="267">
+        <v>390</v>
+      </c>
+      <c r="E6" t="n" s="267">
+        <v>39.0</v>
+      </c>
+      <c r="F6" t="s" s="267">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7" ht="25.0" customHeight="true">
+      <c r="A7" t="s" s="270">
+        <v>104</v>
+      </c>
+      <c r="B7" t="n" s="270">
+        <v>31274.0</v>
+      </c>
+      <c r="C7" t="n" s="270">
+        <v>27392.0</v>
+      </c>
+      <c r="D7" t="s" s="270">
+        <v>333</v>
+      </c>
+      <c r="E7" t="n" s="270">
+        <v>3882.0</v>
+      </c>
+      <c r="F7" t="s" s="270">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" ht="25.0" customHeight="true">
+      <c r="A8" t="s" s="271">
+        <v>185</v>
+      </c>
+      <c r="B8" t="n" s="271">
+        <v>17856.0</v>
+      </c>
+      <c r="C8" t="n" s="271">
+        <v>19729.0</v>
+      </c>
+      <c r="D8" t="s" s="271">
+        <v>390</v>
+      </c>
+      <c r="E8" t="n" s="271">
+        <v>1873.0</v>
+      </c>
+      <c r="F8" t="s" s="271">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="9" ht="25.0" customHeight="true">
+      <c r="A9" t="s" s="280">
+        <v>155</v>
+      </c>
+      <c r="B9" t="n" s="280">
+        <v>22590.0</v>
+      </c>
+      <c r="C9" t="n" s="280">
+        <v>19625.0</v>
+      </c>
+      <c r="D9" t="s" s="280">
+        <v>333</v>
+      </c>
+      <c r="E9" t="n" s="280">
+        <v>2965.0</v>
+      </c>
+      <c r="F9" t="s" s="280">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" ht="25.0" customHeight="true">
+      <c r="A10" t="s" s="283">
+        <v>159</v>
+      </c>
+      <c r="B10" t="n" s="283">
+        <v>16716.0</v>
+      </c>
+      <c r="C10" t="n" s="283">
+        <v>21127.0</v>
+      </c>
+      <c r="D10" t="s" s="283">
+        <v>390</v>
+      </c>
+      <c r="E10" t="n" s="283">
+        <v>4411.0</v>
+      </c>
+      <c r="F10" t="s" s="283">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="11" ht="25.0" customHeight="true">
+      <c r="A11" t="s" s="286">
+        <v>164</v>
+      </c>
+      <c r="B11" t="n" s="286">
+        <v>18422.0</v>
+      </c>
+      <c r="C11" t="n" s="286">
+        <v>17728.0</v>
+      </c>
+      <c r="D11" t="s" s="286">
+        <v>333</v>
+      </c>
+      <c r="E11" t="n" s="286">
+        <v>694.0</v>
+      </c>
+      <c r="F11" t="s" s="286">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" ht="25.0" customHeight="true">
+      <c r="A12" t="s" s="289">
+        <v>167</v>
+      </c>
+      <c r="B12" t="n" s="289">
+        <v>13781.0</v>
+      </c>
+      <c r="C12" t="n" s="289">
+        <v>15796.0</v>
+      </c>
+      <c r="D12" t="s" s="289">
+        <v>390</v>
+      </c>
+      <c r="E12" t="n" s="289">
+        <v>2015.0</v>
+      </c>
+      <c r="F12" t="s" s="289">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="13" ht="25.0" customHeight="true">
+      <c r="A13" t="s" s="292">
+        <v>169</v>
+      </c>
+      <c r="B13" t="n" s="292">
+        <v>15732.0</v>
+      </c>
+      <c r="C13" t="n" s="292">
+        <v>15505.0</v>
+      </c>
+      <c r="D13" t="s" s="292">
+        <v>333</v>
+      </c>
+      <c r="E13" t="n" s="292">
+        <v>227.0</v>
+      </c>
+      <c r="F13" t="s" s="292">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="14" ht="25.0" customHeight="true">
+      <c r="A14" t="s" s="295">
         <v>180</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>642</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>334</v>
+      <c r="B14" t="n" s="295">
+        <v>16003.0</v>
+      </c>
+      <c r="C14" t="n" s="295">
+        <v>12336.0</v>
+      </c>
+      <c r="D14" t="s" s="295">
+        <v>333</v>
+      </c>
+      <c r="E14" t="n" s="295">
+        <v>3667.0</v>
+      </c>
+      <c r="F14" t="s" s="295">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="15" ht="25.0" customHeight="true">
+      <c r="A15" t="s" s="296">
+        <v>199</v>
+      </c>
+      <c r="B15" t="n" s="296">
+        <v>15079.0</v>
+      </c>
+      <c r="C15" t="n" s="296">
+        <v>10067.0</v>
+      </c>
+      <c r="D15" t="s" s="296">
+        <v>333</v>
+      </c>
+      <c r="E15" t="n" s="296">
+        <v>5012.0</v>
+      </c>
+      <c r="F15" t="s" s="296">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="16" ht="25.0" customHeight="true">
+      <c r="A16" t="s" s="297">
+        <v>202</v>
+      </c>
+      <c r="B16" t="n" s="297">
+        <v>13154.0</v>
+      </c>
+      <c r="C16" t="n" s="297">
+        <v>12723.0</v>
+      </c>
+      <c r="D16" t="s" s="297">
+        <v>333</v>
+      </c>
+      <c r="E16" t="n" s="297">
+        <v>431.0</v>
+      </c>
+      <c r="F16" t="s" s="297">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="17" ht="25.0" customHeight="true">
+      <c r="A17" t="s" s="298">
+        <v>205</v>
+      </c>
+      <c r="B17" t="n" s="298">
+        <v>12882.0</v>
+      </c>
+      <c r="C17" t="n" s="298">
+        <v>12665.0</v>
+      </c>
+      <c r="D17" t="s" s="298">
+        <v>333</v>
+      </c>
+      <c r="E17" t="n" s="298">
+        <v>217.0</v>
+      </c>
+      <c r="F17" t="s" s="298">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="18" ht="25.0" customHeight="true">
+      <c r="A18" t="s" s="299">
+        <v>209</v>
+      </c>
+      <c r="B18" t="n" s="299">
+        <v>13077.0</v>
+      </c>
+      <c r="C18" t="n" s="299">
+        <v>12898.0</v>
+      </c>
+      <c r="D18" t="s" s="299">
+        <v>333</v>
+      </c>
+      <c r="E18" t="n" s="299">
+        <v>179.0</v>
+      </c>
+      <c r="F18" t="s" s="299">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" ht="25.0" customHeight="true">
+      <c r="A19" t="s" s="300">
+        <v>212</v>
+      </c>
+      <c r="B19" t="n" s="300">
+        <v>14100.0</v>
+      </c>
+      <c r="C19" t="n" s="300">
+        <v>13913.0</v>
+      </c>
+      <c r="D19" t="s" s="300">
+        <v>333</v>
+      </c>
+      <c r="E19" t="n" s="300">
+        <v>187.0</v>
+      </c>
+      <c r="F19" t="s" s="300">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="20" ht="25.0" customHeight="true">
+      <c r="A20" t="s" s="301">
+        <v>214</v>
+      </c>
+      <c r="B20" t="n" s="301">
+        <v>16797.0</v>
+      </c>
+      <c r="C20" t="n" s="301">
+        <v>14242.0</v>
+      </c>
+      <c r="D20" t="s" s="301">
+        <v>333</v>
+      </c>
+      <c r="E20" t="n" s="301">
+        <v>2555.0</v>
+      </c>
+      <c r="F20" t="s" s="301">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="21" ht="25.0" customHeight="true">
+      <c r="A21" t="s" s="302">
+        <v>218</v>
+      </c>
+      <c r="B21" t="n" s="302">
+        <v>24868.0</v>
+      </c>
+      <c r="C21" t="n" s="302">
+        <v>21427.0</v>
+      </c>
+      <c r="D21" t="s" s="302">
+        <v>333</v>
+      </c>
+      <c r="E21" t="n" s="302">
+        <v>3441.0</v>
+      </c>
+      <c r="F21" t="s" s="302">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="22" ht="25.0" customHeight="true">
+      <c r="A22" t="s" s="304">
+        <v>222</v>
+      </c>
+      <c r="B22" t="n" s="304">
+        <v>21981.0</v>
+      </c>
+      <c r="C22" t="n" s="304">
+        <v>17253.0</v>
+      </c>
+      <c r="D22" t="s" s="304">
+        <v>333</v>
+      </c>
+      <c r="E22" t="n" s="304">
+        <v>4728.0</v>
+      </c>
+      <c r="F22" t="s" s="304">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="23" ht="25.0" customHeight="true">
+      <c r="A23" t="s" s="308">
+        <v>245</v>
+      </c>
+      <c r="B23" t="n" s="308">
+        <v>17154.0</v>
+      </c>
+      <c r="C23" t="n" s="308">
+        <v>12878.0</v>
+      </c>
+      <c r="D23" t="s" s="308">
+        <v>333</v>
+      </c>
+      <c r="E23" t="n" s="308">
+        <v>4276.0</v>
+      </c>
+      <c r="F23" t="s" s="308">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="24" ht="25.0" customHeight="true">
+      <c r="A24" t="s" s="311">
+        <v>248</v>
+      </c>
+      <c r="B24" t="n" s="311">
+        <v>15510.0</v>
+      </c>
+      <c r="C24" t="n" s="311">
+        <v>13533.0</v>
+      </c>
+      <c r="D24" t="s" s="311">
+        <v>333</v>
+      </c>
+      <c r="E24" t="n" s="311">
+        <v>1977.0</v>
+      </c>
+      <c r="F24" t="s" s="311">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" ht="25.0" customHeight="true">
+      <c r="A25" t="s" s="314">
+        <v>251</v>
+      </c>
+      <c r="B25" t="n" s="314">
+        <v>17964.0</v>
+      </c>
+      <c r="C25" t="n" s="314">
+        <v>15973.0</v>
+      </c>
+      <c r="D25" t="s" s="314">
+        <v>333</v>
+      </c>
+      <c r="E25" t="n" s="314">
+        <v>1991.0</v>
+      </c>
+      <c r="F25" t="s" s="314">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="26" ht="25.0" customHeight="true">
+      <c r="A26" t="s" s="316">
+        <v>255</v>
+      </c>
+      <c r="B26" t="n" s="316">
+        <v>11614.0</v>
+      </c>
+      <c r="C26" t="n" s="316">
+        <v>12463.0</v>
+      </c>
+      <c r="D26" t="s" s="316">
+        <v>390</v>
+      </c>
+      <c r="E26" t="n" s="316">
+        <v>849.0</v>
+      </c>
+      <c r="F26" t="s" s="316">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="27" ht="25.0" customHeight="true">
+      <c r="A27" t="s" s="318">
+        <v>257</v>
+      </c>
+      <c r="B27" t="n" s="318">
+        <v>11753.0</v>
+      </c>
+      <c r="C27" t="n" s="318">
+        <v>12225.0</v>
+      </c>
+      <c r="D27" t="s" s="318">
+        <v>390</v>
+      </c>
+      <c r="E27" t="n" s="318">
+        <v>472.0</v>
+      </c>
+      <c r="F27" t="s" s="318">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" ht="25.0" customHeight="true">
+      <c r="A28" t="s" s="320">
+        <v>284</v>
+      </c>
+      <c r="B28" t="n" s="320">
+        <v>10795.0</v>
+      </c>
+      <c r="C28" t="n" s="320">
+        <v>14004.0</v>
+      </c>
+      <c r="D28" t="s" s="320">
+        <v>390</v>
+      </c>
+      <c r="E28" t="n" s="320">
+        <v>3209.0</v>
+      </c>
+      <c r="F28" t="s" s="320">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="29" ht="25.0" customHeight="true">
+      <c r="A29" t="s" s="322">
+        <v>293</v>
+      </c>
+      <c r="B29" t="n" s="322">
+        <v>8783.0</v>
+      </c>
+      <c r="C29" t="n" s="322">
+        <v>8326.0</v>
+      </c>
+      <c r="D29" t="s" s="322">
+        <v>333</v>
+      </c>
+      <c r="E29" t="n" s="322">
+        <v>457.0</v>
+      </c>
+      <c r="F29" t="s" s="322">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="30" ht="25.0" customHeight="true">
+      <c r="A30" t="s" s="325">
+        <v>261</v>
+      </c>
+      <c r="B30" t="n" s="325">
+        <v>9193.0</v>
+      </c>
+      <c r="C30" t="n" s="325">
+        <v>11949.0</v>
+      </c>
+      <c r="D30" t="s" s="325">
+        <v>390</v>
+      </c>
+      <c r="E30" t="n" s="325">
+        <v>2756.0</v>
+      </c>
+      <c r="F30" t="s" s="325">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="31" ht="25.0" customHeight="true">
+      <c r="A31" t="s" s="327">
+        <v>264</v>
+      </c>
+      <c r="B31" t="n" s="327">
+        <v>7385.0</v>
+      </c>
+      <c r="C31" t="n" s="327">
+        <v>11479.0</v>
+      </c>
+      <c r="D31" t="s" s="327">
+        <v>390</v>
+      </c>
+      <c r="E31" t="n" s="327">
+        <v>4094.0</v>
+      </c>
+      <c r="F31" t="s" s="327">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="32" ht="25.0" customHeight="true">
+      <c r="A32" t="s" s="329">
+        <v>267</v>
+      </c>
+      <c r="B32" t="n" s="329">
+        <v>10253.0</v>
+      </c>
+      <c r="C32" t="n" s="329">
+        <v>13270.0</v>
+      </c>
+      <c r="D32" t="s" s="329">
+        <v>390</v>
+      </c>
+      <c r="E32" t="n" s="329">
+        <v>3017.0</v>
+      </c>
+      <c r="F32" t="s" s="329">
+        <v>641</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="20.0"/>
+    <col min="2" max="2" customWidth="true" width="20.0"/>
+    <col min="3" max="3" customWidth="true" width="50.0"/>
+    <col min="4" max="4" customWidth="true" width="50.0"/>
+    <col min="5" max="5" customWidth="true" width="15.0"/>
+    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="7" max="7" customWidth="true" width="12.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="255">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="255">
+        <v>327</v>
+      </c>
+      <c r="C1" t="s" s="255">
+        <v>328</v>
+      </c>
+      <c r="D1" t="s" s="255">
+        <v>329</v>
+      </c>
+      <c r="E1" t="s" s="255">
+        <v>330</v>
+      </c>
+      <c r="F1" t="s" s="255">
+        <v>331</v>
+      </c>
+      <c r="G1" t="s" s="255">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" ht="35.0" customHeight="true">
+      <c r="A2" t="s" s="256">
+        <v>225</v>
+      </c>
+      <c r="B2" t="s" s="256">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s" s="256">
+        <v>335</v>
+      </c>
+      <c r="D2" t="s" s="256">
+        <v>336</v>
+      </c>
+      <c r="E2" t="s" s="256">
+        <v>337</v>
+      </c>
+      <c r="F2" t="s" s="256">
+        <v>573</v>
+      </c>
+      <c r="G2" t="s" s="256">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="35.0" customHeight="true">
+      <c r="A3" t="s" s="257">
+        <v>225</v>
+      </c>
+      <c r="B3" t="s" s="257">
+        <v>229</v>
+      </c>
+      <c r="C3" t="s" s="257">
+        <v>335</v>
+      </c>
+      <c r="D3" t="s" s="257">
+        <v>336</v>
+      </c>
+      <c r="E3" t="s" s="257">
+        <v>337</v>
+      </c>
+      <c r="F3" t="s" s="257">
+        <v>573</v>
+      </c>
+      <c r="G3" t="s" s="257">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" ht="35.0" customHeight="true">
+      <c r="A4" t="s" s="259">
+        <v>225</v>
+      </c>
+      <c r="B4" t="s" s="259">
+        <v>229</v>
+      </c>
+      <c r="C4" t="s" s="259">
+        <v>335</v>
+      </c>
+      <c r="D4" t="s" s="259">
+        <v>336</v>
+      </c>
+      <c r="E4" t="s" s="259">
+        <v>337</v>
+      </c>
+      <c r="F4" t="s" s="259">
+        <v>575</v>
+      </c>
+      <c r="G4" t="s" s="259">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="35.0" customHeight="true">
+      <c r="A5" t="s" s="260">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s" s="260">
+        <v>229</v>
+      </c>
+      <c r="C5" t="s" s="260">
+        <v>335</v>
+      </c>
+      <c r="D5" t="s" s="260">
+        <v>336</v>
+      </c>
+      <c r="E5" t="s" s="260">
+        <v>337</v>
+      </c>
+      <c r="F5" t="s" s="260">
+        <v>576</v>
+      </c>
+      <c r="G5" t="s" s="260">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="35.0" customHeight="true">
+      <c r="A6" t="s" s="262">
+        <v>230</v>
+      </c>
+      <c r="B6" t="s" s="262">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s" s="262">
+        <v>346</v>
+      </c>
+      <c r="D6" t="s" s="262">
+        <v>347</v>
+      </c>
+      <c r="E6" t="s" s="262">
+        <v>337</v>
+      </c>
+      <c r="F6" t="s" s="262">
+        <v>578</v>
+      </c>
+      <c r="G6" t="s" s="262">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" ht="35.0" customHeight="true">
+      <c r="A7" t="s" s="263">
+        <v>230</v>
+      </c>
+      <c r="B7" t="s" s="263">
+        <v>229</v>
+      </c>
+      <c r="C7" t="s" s="263">
+        <v>346</v>
+      </c>
+      <c r="D7" t="s" s="263">
+        <v>347</v>
+      </c>
+      <c r="E7" t="s" s="263">
+        <v>337</v>
+      </c>
+      <c r="F7" t="s" s="263">
+        <v>579</v>
+      </c>
+      <c r="G7" t="s" s="263">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" ht="35.0" customHeight="true">
+      <c r="A8" t="s" s="265">
+        <v>237</v>
+      </c>
+      <c r="B8" t="s" s="265">
+        <v>229</v>
+      </c>
+      <c r="C8" t="s" s="265">
+        <v>350</v>
+      </c>
+      <c r="D8" t="s" s="265">
+        <v>351</v>
+      </c>
+      <c r="E8" t="s" s="265">
+        <v>337</v>
+      </c>
+      <c r="F8" t="s" s="265">
+        <v>581</v>
+      </c>
+      <c r="G8" t="s" s="265">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" ht="35.0" customHeight="true">
+      <c r="A9" t="s" s="266">
+        <v>237</v>
+      </c>
+      <c r="B9" t="s" s="266">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s" s="266">
+        <v>350</v>
+      </c>
+      <c r="D9" t="s" s="266">
+        <v>351</v>
+      </c>
+      <c r="E9" t="s" s="266">
+        <v>337</v>
+      </c>
+      <c r="F9" t="s" s="266">
+        <v>582</v>
+      </c>
+      <c r="G9" t="s" s="266">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6197,194 +7428,195 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="35.0"/>
+    <col min="2" max="2" customWidth="true" width="12.0"/>
+    <col min="3" max="3" customWidth="true" width="15.0"/>
+    <col min="4" max="4" customWidth="true" width="12.0"/>
+    <col min="5" max="5" customWidth="true" width="25.0"/>
+    <col min="6" max="6" customWidth="true" width="12.0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>643</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>644</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>645</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>646</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>647</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>648</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>649</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>650</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>651</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>653</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>334</v>
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="76">
+        <v>392</v>
+      </c>
+      <c r="B1" t="s" s="76">
+        <v>356</v>
+      </c>
+      <c r="C1" t="s" s="76">
+        <v>393</v>
+      </c>
+      <c r="D1" t="s" s="76">
+        <v>394</v>
+      </c>
+      <c r="E1" t="s" s="76">
+        <v>331</v>
+      </c>
+      <c r="F1" t="s" s="76">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="272">
+        <v>192</v>
+      </c>
+      <c r="B2" t="s" s="272">
+        <v>360</v>
+      </c>
+      <c r="C2" t="s" s="272">
+        <v>396</v>
+      </c>
+      <c r="D2" t="n" s="272">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="272">
+        <v>588</v>
+      </c>
+      <c r="F2" t="s" s="272">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="273">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s" s="273">
+        <v>360</v>
+      </c>
+      <c r="C3" t="s" s="273">
+        <v>396</v>
+      </c>
+      <c r="D3" t="n" s="273">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="273">
+        <v>589</v>
+      </c>
+      <c r="F3" t="s" s="273">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" ht="25.0" customHeight="true">
+      <c r="A4" t="s" s="274">
+        <v>192</v>
+      </c>
+      <c r="B4" t="s" s="274">
+        <v>360</v>
+      </c>
+      <c r="C4" t="s" s="274">
+        <v>396</v>
+      </c>
+      <c r="D4" t="n" s="274">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s" s="274">
+        <v>589</v>
+      </c>
+      <c r="F4" t="s" s="274">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="25.0" customHeight="true">
+      <c r="A5" t="s" s="275">
+        <v>192</v>
+      </c>
+      <c r="B5" t="s" s="275">
+        <v>360</v>
+      </c>
+      <c r="C5" t="s" s="275">
+        <v>399</v>
+      </c>
+      <c r="D5" t="n" s="275">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="s" s="275">
+        <v>590</v>
+      </c>
+      <c r="F5" t="s" s="275">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" ht="25.0" customHeight="true">
+      <c r="A6" t="s" s="276">
+        <v>192</v>
+      </c>
+      <c r="B6" t="s" s="276">
+        <v>360</v>
+      </c>
+      <c r="C6" t="s" s="276">
+        <v>396</v>
+      </c>
+      <c r="D6" t="n" s="276">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="s" s="276">
+        <v>591</v>
+      </c>
+      <c r="F6" t="s" s="276">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" ht="25.0" customHeight="true">
+      <c r="A7" t="s" s="277">
+        <v>192</v>
+      </c>
+      <c r="B7" t="s" s="277">
+        <v>360</v>
+      </c>
+      <c r="C7" t="s" s="277">
+        <v>396</v>
+      </c>
+      <c r="D7" t="n" s="277">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s" s="277">
+        <v>592</v>
+      </c>
+      <c r="F7" t="s" s="277">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" ht="25.0" customHeight="true">
+      <c r="A8" t="s" s="278">
+        <v>192</v>
+      </c>
+      <c r="B8" t="s" s="278">
+        <v>360</v>
+      </c>
+      <c r="C8" t="s" s="278">
+        <v>396</v>
+      </c>
+      <c r="D8" t="n" s="278">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s" s="278">
+        <v>592</v>
+      </c>
+      <c r="F8" t="s" s="278">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" ht="25.0" customHeight="true">
+      <c r="A9" t="s" s="279">
+        <v>192</v>
+      </c>
+      <c r="B9" t="s" s="279">
+        <v>360</v>
+      </c>
+      <c r="C9" t="s" s="279">
+        <v>399</v>
+      </c>
+      <c r="D9" t="n" s="279">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s" s="279">
+        <v>593</v>
+      </c>
+      <c r="F9" t="s" s="279">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6394,214 +7626,297 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="18.0"/>
+    <col min="2" max="2" customWidth="true" width="20.0"/>
+    <col min="3" max="3" customWidth="true" width="20.0"/>
+    <col min="4" max="4" customWidth="true" width="15.0"/>
+    <col min="5" max="5" customWidth="true" width="12.0"/>
+    <col min="6" max="6" customWidth="true" width="40.0"/>
+    <col min="7" max="7" customWidth="true" width="25.0"/>
+    <col min="8" max="8" customWidth="true" width="12.0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="82">
         <v>69</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s" s="82">
         <v>401</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s" s="82">
         <v>402</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s" s="82">
         <v>403</v>
       </c>
-      <c r="E1" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C2" t="s" s="0">
+      <c r="E1" t="s" s="82">
+        <v>330</v>
+      </c>
+      <c r="F1" t="s" s="82">
         <v>404</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>621</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>622</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>623</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>624</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="D6" t="s" s="0">
+      <c r="G1" t="s" s="82">
+        <v>331</v>
+      </c>
+      <c r="H1" t="s" s="82">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="281">
+        <v>159</v>
+      </c>
+      <c r="B2" t="s" s="281">
         <v>409</v>
       </c>
-      <c r="E6" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>625</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="D7" t="s" s="0">
+      <c r="C2" t="s" s="281">
+        <v>410</v>
+      </c>
+      <c r="D2" t="s" s="281">
+        <v>411</v>
+      </c>
+      <c r="E2" t="s" s="281">
+        <v>337</v>
+      </c>
+      <c r="F2" t="s" s="281">
+        <v>412</v>
+      </c>
+      <c r="G2" t="s" s="281">
+        <v>595</v>
+      </c>
+      <c r="H2" t="s" s="281">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="282">
+        <v>159</v>
+      </c>
+      <c r="B3" t="s" s="282">
         <v>409</v>
       </c>
-      <c r="E7" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>626</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C8" t="s" s="0">
+      <c r="C3" t="s" s="282">
+        <v>410</v>
+      </c>
+      <c r="D3" t="s" s="282">
         <v>411</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="E3" t="s" s="282">
+        <v>337</v>
+      </c>
+      <c r="F3" t="s" s="282">
         <v>412</v>
       </c>
-      <c r="E8" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>627</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C9" t="s" s="0">
+      <c r="G3" t="s" s="282">
+        <v>596</v>
+      </c>
+      <c r="H3" t="s" s="282">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" ht="25.0" customHeight="true">
+      <c r="A4" t="s" s="284">
+        <v>164</v>
+      </c>
+      <c r="B4" s="284"/>
+      <c r="C4" t="s" s="284">
+        <v>410</v>
+      </c>
+      <c r="D4" t="s" s="284">
         <v>411</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>412</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>628</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>334</v>
+      <c r="E4" t="s" s="284">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s" s="284">
+        <v>415</v>
+      </c>
+      <c r="G4" t="s" s="284">
+        <v>598</v>
+      </c>
+      <c r="H4" t="s" s="284">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="25.0" customHeight="true">
+      <c r="A5" t="s" s="285">
+        <v>164</v>
+      </c>
+      <c r="B5" s="285"/>
+      <c r="C5" t="s" s="285">
+        <v>410</v>
+      </c>
+      <c r="D5" t="s" s="285">
+        <v>411</v>
+      </c>
+      <c r="E5" t="s" s="285">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s" s="285">
+        <v>415</v>
+      </c>
+      <c r="G5" t="s" s="285">
+        <v>599</v>
+      </c>
+      <c r="H5" t="s" s="285">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="25.0" customHeight="true">
+      <c r="A6" t="s" s="287">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s" s="287">
+        <v>409</v>
+      </c>
+      <c r="C6" s="287"/>
+      <c r="D6" t="s" s="287">
+        <v>411</v>
+      </c>
+      <c r="E6" t="s" s="287">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s" s="287">
+        <v>419</v>
+      </c>
+      <c r="G6" t="s" s="287">
+        <v>601</v>
+      </c>
+      <c r="H6" t="s" s="287">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" ht="25.0" customHeight="true">
+      <c r="A7" t="s" s="288">
+        <v>167</v>
+      </c>
+      <c r="B7" t="s" s="288">
+        <v>409</v>
+      </c>
+      <c r="C7" s="288"/>
+      <c r="D7" t="s" s="288">
+        <v>411</v>
+      </c>
+      <c r="E7" t="s" s="288">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s" s="288">
+        <v>419</v>
+      </c>
+      <c r="G7" t="s" s="288">
+        <v>602</v>
+      </c>
+      <c r="H7" t="s" s="288">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" ht="25.0" customHeight="true">
+      <c r="A8" t="s" s="290">
+        <v>169</v>
+      </c>
+      <c r="B8" t="s" s="290">
+        <v>409</v>
+      </c>
+      <c r="C8" t="s" s="290">
+        <v>410</v>
+      </c>
+      <c r="D8" s="290"/>
+      <c r="E8" t="s" s="290">
+        <v>414</v>
+      </c>
+      <c r="F8" t="s" s="290">
+        <v>423</v>
+      </c>
+      <c r="G8" t="s" s="290">
+        <v>604</v>
+      </c>
+      <c r="H8" t="s" s="290">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" ht="25.0" customHeight="true">
+      <c r="A9" t="s" s="291">
+        <v>169</v>
+      </c>
+      <c r="B9" t="s" s="291">
+        <v>409</v>
+      </c>
+      <c r="C9" t="s" s="291">
+        <v>410</v>
+      </c>
+      <c r="D9" s="291"/>
+      <c r="E9" t="s" s="291">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s" s="291">
+        <v>423</v>
+      </c>
+      <c r="G9" t="s" s="291">
+        <v>605</v>
+      </c>
+      <c r="H9" t="s" s="291">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="20.0"/>
+    <col min="2" max="2" customWidth="true" width="15.0"/>
+    <col min="3" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="12.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.0" customHeight="true">
+      <c r="A1" t="s" s="96">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s" s="96">
+        <v>330</v>
+      </c>
+      <c r="C1" t="s" s="96">
+        <v>331</v>
+      </c>
+      <c r="D1" t="s" s="96">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" ht="25.0" customHeight="true">
+      <c r="A2" t="s" s="293">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s" s="293">
+        <v>337</v>
+      </c>
+      <c r="C2" t="s" s="293">
+        <v>607</v>
+      </c>
+      <c r="D2" t="s" s="293">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" ht="25.0" customHeight="true">
+      <c r="A3" t="s" s="294">
+        <v>180</v>
+      </c>
+      <c r="B3" t="s" s="294">
+        <v>337</v>
+      </c>
+      <c r="C3" t="s" s="294">
+        <v>608</v>
+      </c>
+      <c r="D3" t="s" s="294">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
